--- a/records/CP_Learning_Record.xlsx
+++ b/records/CP_Learning_Record.xlsx
@@ -1,3 +1,113 @@
+
+<file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
+<x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheets>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reference" sheetId="1" r:id="R6c939c68a10846e2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Assessments" sheetId="2" r:id="R864413c67c8c4c28"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mastery" sheetId="3" r:id="R1c4bc4eb7c2f4168"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decision_Coverage" sheetId="4" r:id="Re2dc3815f65d4c5a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Review_Debt" sheetId="5" r:id="R85a91cf5845541bd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Baseline" sheetId="6" r:id="Rf3945651fec74c83"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mocks" sheetId="7" r:id="R5e0dd23ce331468e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Readiness" sheetId="8" r:id="Rcb24622494c64e6a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="9" r:id="Re767854e900141e7"/>
+  </x:sheets>
+</x:workbook>
+</file>
+
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
+<file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
+<x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:fonts count="2">
+    <x:font>
+      <x:sz val="11"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:color rgb="FFFFFFFF"/>
+      <x:name val="Carlito"/>
+    </x:font>
+  </x:fonts>
+  <x:fills count="3">
+    <x:fill>
+      <x:patternFill patternType="none"/>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="gray125"/>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF1F4E78"/>
+      </x:patternFill>
+    </x:fill>
+  </x:fills>
+  <x:borders count="2">
+    <x:border/>
+    <x:border/>
+  </x:borders>
+  <x:cellStyleXfs count="1">
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  </x:cellStyleXfs>
+  <x:cellXfs count="20">
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+  </x:cellXfs>
+  <x:cellStyles count="1">
+    <x:cellStyle name="Normal" xfId="0"/>
+  </x:cellStyles>
+</x:styleSheet>
+</file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="ChatGPT">
@@ -188,4 +298,1227 @@
     </a:fmtScheme>
   </a:themeElements>
 </a:theme>
+</file>
+
+<file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="24" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="52" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1">
+      <x:c r="A1" s="14" t="str">
+        <x:v>Field</x:v>
+      </x:c>
+      <x:c r="B1" s="14" t="str">
+        <x:v>Allowed / Meaning</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" s="15" t="str">
+        <x:v>Result</x:v>
+      </x:c>
+      <x:c r="B2" s="15" t="str">
+        <x:v>PASS | CONDITIONAL PASS | FAIL | VOID</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" s="15" t="str">
+        <x:v>Validation Tier</x:v>
+      </x:c>
+      <x:c r="B3" s="15" t="str">
+        <x:v>A | B | C</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" s="15" t="str">
+        <x:v>Capability</x:v>
+      </x:c>
+      <x:c r="B4" s="15" t="str">
+        <x:v>L0 | L1 | L2 | L3 | L4 | L5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" s="15" t="str">
+        <x:v>Confidence</x:v>
+      </x:c>
+      <x:c r="B5" s="15" t="str">
+        <x:v>Unverified | Provisional | Confirmed | Stable</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" s="15" t="str">
+        <x:v>Review Debt</x:v>
+      </x:c>
+      <x:c r="B6" s="15" t="str">
+        <x:v>None | Open | Resolved</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" s="15" t="str">
+        <x:v>Review Debt Severity</x:v>
+      </x:c>
+      <x:c r="B7" s="15" t="str">
+        <x:v>N/A | Low | Medium | High</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" s="15" t="str">
+        <x:v>First-pass Correct</x:v>
+      </x:c>
+      <x:c r="B8" s="15" t="str">
+        <x:v>Yes | No | N/A</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" s="15" t="str">
+        <x:v>Hints</x:v>
+      </x:c>
+      <x:c r="B9" s="15" t="str">
+        <x:v>None | Requested | GPT-provided</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" s="15" t="str">
+        <x:v>Formal?</x:v>
+      </x:c>
+      <x:c r="B10" s="15" t="str">
+        <x:v>Yes | No</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="12" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="18" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="30" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="12" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="20" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="8" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="8" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="14" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="25" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="28" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="22" hidden="0" customWidth="1"/>
+    <x:col min="13" max="13" width="20" hidden="0" customWidth="1"/>
+    <x:col min="14" max="14" width="14" hidden="0" customWidth="1"/>
+    <x:col min="15" max="15" width="14" hidden="0" customWidth="1"/>
+    <x:col min="16" max="16" width="16" hidden="0" customWidth="1"/>
+    <x:col min="17" max="17" width="16" hidden="0" customWidth="1"/>
+    <x:col min="18" max="18" width="18" hidden="0" customWidth="1"/>
+    <x:col min="19" max="19" width="14" hidden="0" customWidth="1"/>
+    <x:col min="20" max="20" width="16" hidden="0" customWidth="1"/>
+    <x:col min="21" max="21" width="16" hidden="0" customWidth="1"/>
+    <x:col min="22" max="22" width="14" hidden="0" customWidth="1"/>
+    <x:col min="23" max="23" width="16" hidden="0" customWidth="1"/>
+    <x:col min="24" max="24" width="22" hidden="0" customWidth="1"/>
+    <x:col min="25" max="25" width="30" hidden="0" customWidth="1"/>
+    <x:col min="26" max="26" width="16" hidden="0" customWidth="1"/>
+    <x:col min="27" max="27" width="18" hidden="0" customWidth="1"/>
+    <x:col min="28" max="28" width="20" hidden="0" customWidth="1"/>
+    <x:col min="29" max="29" width="14" hidden="0" customWidth="1"/>
+    <x:col min="30" max="30" width="18" hidden="0" customWidth="1"/>
+    <x:col min="31" max="31" width="16" hidden="0" customWidth="1"/>
+    <x:col min="32" max="32" width="45" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1">
+      <x:c r="A1" s="14" t="str">
+        <x:v>Date</x:v>
+      </x:c>
+      <x:c r="B1" s="14" t="str">
+        <x:v>Learning Unit</x:v>
+      </x:c>
+      <x:c r="C1" s="14" t="str">
+        <x:v>Assessment Type</x:v>
+      </x:c>
+      <x:c r="D1" s="14" t="str">
+        <x:v>Problem</x:v>
+      </x:c>
+      <x:c r="E1" s="14" t="str">
+        <x:v>Validation Tier</x:v>
+      </x:c>
+      <x:c r="F1" s="14" t="str">
+        <x:v>Validation Evidence</x:v>
+      </x:c>
+      <x:c r="G1" s="14" t="str">
+        <x:v>R</x:v>
+      </x:c>
+      <x:c r="H1" s="14" t="str">
+        <x:v>I</x:v>
+      </x:c>
+      <x:c r="I1" s="14" t="str">
+        <x:v>Calibration</x:v>
+      </x:c>
+      <x:c r="J1" s="14" t="str">
+        <x:v>Calibration Registry</x:v>
+      </x:c>
+      <x:c r="K1" s="14" t="str">
+        <x:v>Core Decision Boundary Coverage</x:v>
+      </x:c>
+      <x:c r="L1" s="14" t="str">
+        <x:v>Unit Coverage Status</x:v>
+      </x:c>
+      <x:c r="M1" s="14" t="str">
+        <x:v>Mode</x:v>
+      </x:c>
+      <x:c r="N1" s="14" t="str">
+        <x:v>Time Limit (min)</x:v>
+      </x:c>
+      <x:c r="O1" s="14" t="str">
+        <x:v>T_solve (min)</x:v>
+      </x:c>
+      <x:c r="P1" s="14" t="str">
+        <x:v>T_recognition (min)</x:v>
+      </x:c>
+      <x:c r="Q1" s="14" t="str">
+        <x:v>T_implementation (min)</x:v>
+      </x:c>
+      <x:c r="R1" s="14" t="str">
+        <x:v>T_validation_debug (min)</x:v>
+      </x:c>
+      <x:c r="S1" s="14" t="str">
+        <x:v>T_explain (min)</x:v>
+      </x:c>
+      <x:c r="T1" s="14" t="str">
+        <x:v>Compile/Run/Submit Count</x:v>
+      </x:c>
+      <x:c r="U1" s="14" t="str">
+        <x:v>First-pass Correct</x:v>
+      </x:c>
+      <x:c r="V1" s="14" t="str">
+        <x:v>Hints</x:v>
+      </x:c>
+      <x:c r="W1" s="14" t="str">
+        <x:v>Result</x:v>
+      </x:c>
+      <x:c r="X1" s="14" t="str">
+        <x:v>Failure Attribution</x:v>
+      </x:c>
+      <x:c r="Y1" s="14" t="str">
+        <x:v>Error Types</x:v>
+      </x:c>
+      <x:c r="Z1" s="14" t="str">
+        <x:v>Capability Level</x:v>
+      </x:c>
+      <x:c r="AA1" s="14" t="str">
+        <x:v>Confidence Status</x:v>
+      </x:c>
+      <x:c r="AB1" s="14" t="str">
+        <x:v>Evidence Context</x:v>
+      </x:c>
+      <x:c r="AC1" s="14" t="str">
+        <x:v>Review Debt</x:v>
+      </x:c>
+      <x:c r="AD1" s="14" t="str">
+        <x:v>Review Debt Severity</x:v>
+      </x:c>
+      <x:c r="AE1" s="14" t="str">
+        <x:v>Retest Needed</x:v>
+      </x:c>
+      <x:c r="AF1" s="14" t="str">
+        <x:v>Notes</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" s="15" t="str">
+        <x:v>2026-09-11</x:v>
+      </x:c>
+      <x:c r="B2" s="15" t="str">
+        <x:v>S0-A — C++ Basic Execution</x:v>
+      </x:c>
+      <x:c r="C2" s="15" t="str">
+        <x:v>Intermediate Assessment — Attempt 1</x:v>
+      </x:c>
+      <x:c r="D2" s="15" t="str">
+        <x:v>Count and sum positive multiples of 3</x:v>
+      </x:c>
+      <x:c r="E2" s="15" t="str">
+        <x:v>C</x:v>
+      </x:c>
+      <x:c r="F2" s="15" t="str">
+        <x:v>Reasoning-only; Tier B pre-validation not completed before exposure</x:v>
+      </x:c>
+      <x:c r="G2" s="15" t="str">
+        <x:v>R1</x:v>
+      </x:c>
+      <x:c r="H2" s="15" t="str">
+        <x:v>I1</x:v>
+      </x:c>
+      <x:c r="I2" s="15" t="str">
+        <x:v>Comparative / Provisional</x:v>
+      </x:c>
+      <x:c r="J2" s="15" t="str">
+        <x:v>CP_Calibration_Anchor_Registry_v1.1</x:v>
+      </x:c>
+      <x:c r="K2" s="15" t="str">
+        <x:v>Basic execution: input + condition + loop + function</x:v>
+      </x:c>
+      <x:c r="L2" s="15" t="str">
+        <x:v>Incomplete</x:v>
+      </x:c>
+      <x:c r="M2" s="15" t="str">
+        <x:v>Immediate</x:v>
+      </x:c>
+      <x:c r="O2" s="15" t="n">
+        <x:v>9.166666666666666</x:v>
+      </x:c>
+      <x:c r="U2" s="15" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="V2" s="15" t="str">
+        <x:v>GPT-provided</x:v>
+      </x:c>
+      <x:c r="W2" s="15" t="str">
+        <x:v>VOID</x:v>
+      </x:c>
+      <x:c r="X2" s="15" t="str">
+        <x:v>N/A</x:v>
+      </x:c>
+      <x:c r="Y2" s="15" t="str">
+        <x:v>missing input read for N; required helper function absent; no edge-case validation</x:v>
+      </x:c>
+      <x:c r="Z2" s="15" t="str">
+        <x:v>L2</x:v>
+      </x:c>
+      <x:c r="AA2" s="15" t="str">
+        <x:v>Provisional</x:v>
+      </x:c>
+      <x:c r="AB2" s="15" t="str">
+        <x:v>Baseline; Immediate diagnostic (VOID, not mastery evidence)</x:v>
+      </x:c>
+      <x:c r="AC2" s="15" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="AD2" s="15" t="str">
+        <x:v>N/A</x:v>
+      </x:c>
+      <x:c r="AE2" s="15" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="AF2" s="15" t="str">
+        <x:v>Evaluator-side defect: generated problem was not cross-validated to Tier B before formal use, and the prompt exposed a solution-relevant direction ('process while reading; vector not needed'). Attempt is not formal mastery evidence. Diagnostic only: N remains 0 because cin &gt;&gt; N is missing, so the loop never executes and output is always 0 0; the required non-main function was not implemented. The stated O(N)/O(1) complexity describes the intended design after fixing input, not the submitted program.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" t="str">
+        <x:v>2026-09-11</x:v>
+      </x:c>
+      <x:c r="B3" t="str">
+        <x:v>S0-A — C++ Basic Execution</x:v>
+      </x:c>
+      <x:c r="C3" t="str">
+        <x:v>Intermediate Assessment — Retest 1</x:v>
+      </x:c>
+      <x:c r="D3" t="str">
+        <x:v>Transform and sum by sign/parity</x:v>
+      </x:c>
+      <x:c r="E3" t="str">
+        <x:v>B</x:v>
+      </x:c>
+      <x:c r="F3" t="str">
+        <x:v>Reference execution + boundary tests + randomized differential verification</x:v>
+      </x:c>
+      <x:c r="G3" t="str">
+        <x:v>R1</x:v>
+      </x:c>
+      <x:c r="H3" t="str">
+        <x:v>I1</x:v>
+      </x:c>
+      <x:c r="I3" t="str">
+        <x:v>Comparative / Provisional</x:v>
+      </x:c>
+      <x:c r="J3" t="str">
+        <x:v>CP_Calibration_Anchor_Registry_v1.1</x:v>
+      </x:c>
+      <x:c r="K3" t="str">
+        <x:v>Basic execution: input + conditional branching + loop + helper function + scalar accumulation</x:v>
+      </x:c>
+      <x:c r="L3" t="str">
+        <x:v>Sufficient for Provisional</x:v>
+      </x:c>
+      <x:c r="M3" t="str">
+        <x:v>Immediate</x:v>
+      </x:c>
+      <x:c r="N3"/>
+      <x:c r="O3" t="n">
+        <x:v>4.666666666666667</x:v>
+      </x:c>
+      <x:c r="P3"/>
+      <x:c r="Q3"/>
+      <x:c r="R3"/>
+      <x:c r="S3"/>
+      <x:c r="T3"/>
+      <x:c r="U3" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="V3" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="W3" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="X3" t="str">
+        <x:v>N/A</x:v>
+      </x:c>
+      <x:c r="Y3" t="str">
+        <x:v>No correctness error. Explicit edge-case self-check was not listed.</x:v>
+      </x:c>
+      <x:c r="Z3" t="str">
+        <x:v>L3</x:v>
+      </x:c>
+      <x:c r="AA3" t="str">
+        <x:v>Provisional</x:v>
+      </x:c>
+      <x:c r="AB3" t="str">
+        <x:v>Immediate</x:v>
+      </x:c>
+      <x:c r="AC3" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="AD3" t="str">
+        <x:v>N/A</x:v>
+      </x:c>
+      <x:c r="AE3" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="AF3" t="str">
+        <x:v>Clean independent retest. Submitted program compiles and is correct on the sample, boundary-oriented tests, and randomized differential checks. Required helper function is defined and called. O(N) time and O(1) extra-space explanations are correct. No edge case was explicitly listed, but the implementation handles key categories including x&lt;0, x=0, positive even/odd values, N=1, and input bounds; omission of an explicit self-check is retained as a process note rather than a correctness failure. Proceed to Part F final assessment.</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="10" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="26" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="16" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="12" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="16" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="22" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="14" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="14" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="14" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="14" hidden="0" customWidth="1"/>
+    <x:col min="13" max="13" width="32" hidden="0" customWidth="1"/>
+    <x:col min="14" max="14" width="45" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="42" hidden="0" customHeight="1">
+      <x:c r="A1" s="14" t="str">
+        <x:v>Stage</x:v>
+      </x:c>
+      <x:c r="B1" s="14" t="str">
+        <x:v>Learning Unit</x:v>
+      </x:c>
+      <x:c r="C1" s="14" t="str">
+        <x:v>Priority Class</x:v>
+      </x:c>
+      <x:c r="D1" s="14" t="str">
+        <x:v>Capability</x:v>
+      </x:c>
+      <x:c r="E1" s="14" t="str">
+        <x:v>Confidence</x:v>
+      </x:c>
+      <x:c r="F1" s="14" t="str">
+        <x:v>Evidence Context</x:v>
+      </x:c>
+      <x:c r="G1" s="14" t="str">
+        <x:v>Unit Coverage Status</x:v>
+      </x:c>
+      <x:c r="H1" s="14" t="str">
+        <x:v>Review Debt</x:v>
+      </x:c>
+      <x:c r="I1" s="14" t="str">
+        <x:v>Review Debt Severity</x:v>
+      </x:c>
+      <x:c r="J1" s="14" t="str">
+        <x:v>Retest Needed</x:v>
+      </x:c>
+      <x:c r="K1" s="14" t="str">
+        <x:v>Last Assessed</x:v>
+      </x:c>
+      <x:c r="L1" s="14" t="str">
+        <x:v>Next Review</x:v>
+      </x:c>
+      <x:c r="M1" s="14" t="str">
+        <x:v>Current Bottleneck</x:v>
+      </x:c>
+      <x:c r="N1" s="14" t="str">
+        <x:v>Notes</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" ht="42" hidden="0" customHeight="1">
+      <x:c r="A2" s="18" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="B2" s="18" t="str">
+        <x:v>S0-A — C++ Basic Execution</x:v>
+      </x:c>
+      <x:c r="C2" s="18" t="str">
+        <x:v>Core</x:v>
+      </x:c>
+      <x:c r="D2" s="18" t="str">
+        <x:v>L3</x:v>
+      </x:c>
+      <x:c r="E2" s="18" t="str">
+        <x:v>Provisional</x:v>
+      </x:c>
+      <x:c r="F2" s="18" t="str">
+        <x:v>Immediate</x:v>
+      </x:c>
+      <x:c r="G2" s="18" t="str">
+        <x:v>Sufficient for Provisional</x:v>
+      </x:c>
+      <x:c r="H2" s="18" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="I2" s="18" t="str">
+        <x:v>N/A</x:v>
+      </x:c>
+      <x:c r="J2" s="18" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="K2" s="18" t="str">
+        <x:v>2026-09-11</x:v>
+      </x:c>
+      <x:c r="L2" t="str">
+        <x:v>Final Assessment</x:v>
+      </x:c>
+      <x:c r="M2" s="18" t="str">
+        <x:v>Explicit edge-case self-validation has not yet been demonstrated; final assessment is still required for S0-A completion.</x:v>
+      </x:c>
+      <x:c r="N2" s="18" t="str">
+        <x:v>Clean Part E retest PASS in 4:40. Correct input handling, branching, loop, helper function, scalar accumulation, and O(N)/O(1) analysis. Proceed to Part F.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" ht="42" hidden="0" customHeight="1">
+      <x:c r="A3" s="18" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="B3" s="18" t="str">
+        <x:v>S0-B — Basic Containers &amp; STL</x:v>
+      </x:c>
+      <x:c r="C3" s="18" t="str">
+        <x:v>Core</x:v>
+      </x:c>
+      <x:c r="D3" s="18" t="str">
+        <x:v>L1</x:v>
+      </x:c>
+      <x:c r="E3" s="18" t="str">
+        <x:v>Provisional</x:v>
+      </x:c>
+      <x:c r="F3" s="18" t="str">
+        <x:v>Baseline</x:v>
+      </x:c>
+      <x:c r="G3" s="18" t="str">
+        <x:v>N/A</x:v>
+      </x:c>
+      <x:c r="H3" s="18" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="I3" s="18" t="str">
+        <x:v>N/A</x:v>
+      </x:c>
+      <x:c r="J3" s="18" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="K3" s="18" t="str">
+        <x:v>2026-09-11</x:v>
+      </x:c>
+      <x:c r="M3" s="18" t="str">
+        <x:v>vector construction/manipulation and basic STL syntax are a clear knowledge gap.</x:v>
+      </x:c>
+      <x:c r="N3" s="18" t="str">
+        <x:v>Baseline Problem A/B both exposed vector/STL implementation gaps.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" ht="42" hidden="0" customHeight="1">
+      <x:c r="A4" s="18" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="B4" s="18" t="str">
+        <x:v>S0-C — Complexity &amp; Numeric Safety</x:v>
+      </x:c>
+      <x:c r="C4" s="18" t="str">
+        <x:v>Core</x:v>
+      </x:c>
+      <x:c r="D4" s="18" t="str">
+        <x:v>L2</x:v>
+      </x:c>
+      <x:c r="E4" s="18" t="str">
+        <x:v>Provisional</x:v>
+      </x:c>
+      <x:c r="F4" s="18" t="str">
+        <x:v>Baseline</x:v>
+      </x:c>
+      <x:c r="G4" s="18" t="str">
+        <x:v>N/A</x:v>
+      </x:c>
+      <x:c r="H4" s="18" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="I4" s="18" t="str">
+        <x:v>N/A</x:v>
+      </x:c>
+      <x:c r="J4" s="18" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="K4" s="18" t="str">
+        <x:v>2026-09-11</x:v>
+      </x:c>
+      <x:c r="M4" s="18" t="str">
+        <x:v>Understands O(N log N) loop composition and multiplication overflow, but misclassified sort and failed to apply numeric bounds consistently.</x:v>
+      </x:c>
+      <x:c r="N4" s="18" t="str">
+        <x:v>Needs explicit constraint-to-type and operation-complexity verification habits.</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="10" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="24" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="38" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="22" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="28" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="14" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="45" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1">
+      <x:c r="A1" s="14" t="str">
+        <x:v>Stage</x:v>
+      </x:c>
+      <x:c r="B1" s="14" t="str">
+        <x:v>Learning Unit</x:v>
+      </x:c>
+      <x:c r="C1" s="14" t="str">
+        <x:v>Core Decision Boundary</x:v>
+      </x:c>
+      <x:c r="D1" s="14" t="str">
+        <x:v>Status</x:v>
+      </x:c>
+      <x:c r="E1" s="14" t="str">
+        <x:v>Evidence Context</x:v>
+      </x:c>
+      <x:c r="F1" s="14" t="str">
+        <x:v>Assessment Type</x:v>
+      </x:c>
+      <x:c r="G1" s="14" t="str">
+        <x:v>Problem</x:v>
+      </x:c>
+      <x:c r="H1" s="14" t="str">
+        <x:v>Date</x:v>
+      </x:c>
+      <x:c r="I1" s="14" t="str">
+        <x:v>Notes</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="14" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="10" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="24" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="12" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="36" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="14" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="36" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="14" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="14" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="45" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1">
+      <x:c r="A1" s="14" t="str">
+        <x:v>Opened</x:v>
+      </x:c>
+      <x:c r="B1" s="14" t="str">
+        <x:v>Stage</x:v>
+      </x:c>
+      <x:c r="C1" s="14" t="str">
+        <x:v>Learning Unit</x:v>
+      </x:c>
+      <x:c r="D1" s="14" t="str">
+        <x:v>Severity</x:v>
+      </x:c>
+      <x:c r="E1" s="14" t="str">
+        <x:v>Reason</x:v>
+      </x:c>
+      <x:c r="F1" s="14" t="str">
+        <x:v>Prerequisite Blocking?</x:v>
+      </x:c>
+      <x:c r="G1" s="14" t="str">
+        <x:v>Status</x:v>
+      </x:c>
+      <x:c r="H1" s="14" t="str">
+        <x:v>Next Remediation</x:v>
+      </x:c>
+      <x:c r="I1" s="14" t="str">
+        <x:v>Next Review</x:v>
+      </x:c>
+      <x:c r="J1" s="14" t="str">
+        <x:v>Resolved</x:v>
+      </x:c>
+      <x:c r="K1" s="14" t="str">
+        <x:v>Notes</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="12" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="34" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="14" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="8" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="8" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="18" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="14" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="16" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="16" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="16" hidden="0" customWidth="1"/>
+    <x:col min="13" max="13" width="24" hidden="0" customWidth="1"/>
+    <x:col min="14" max="14" width="38" hidden="0" customWidth="1"/>
+    <x:col min="15" max="15" width="38" hidden="0" customWidth="1"/>
+    <x:col min="16" max="16" width="60" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="36" hidden="0" customHeight="1">
+      <x:c r="A1" s="14" t="str">
+        <x:v>Date</x:v>
+      </x:c>
+      <x:c r="B1" s="14" t="str">
+        <x:v>Block</x:v>
+      </x:c>
+      <x:c r="C1" s="14" t="str">
+        <x:v>Problem</x:v>
+      </x:c>
+      <x:c r="D1" s="14" t="str">
+        <x:v>Validation Tier</x:v>
+      </x:c>
+      <x:c r="E1" s="14" t="str">
+        <x:v>R</x:v>
+      </x:c>
+      <x:c r="F1" s="14" t="str">
+        <x:v>I</x:v>
+      </x:c>
+      <x:c r="G1" s="14" t="str">
+        <x:v>Result</x:v>
+      </x:c>
+      <x:c r="H1" s="14" t="str">
+        <x:v>T_solve (min)</x:v>
+      </x:c>
+      <x:c r="I1" s="14" t="str">
+        <x:v>T_recognition (min)</x:v>
+      </x:c>
+      <x:c r="J1" s="14" t="str">
+        <x:v>T_implementation (min)</x:v>
+      </x:c>
+      <x:c r="K1" s="14" t="str">
+        <x:v>T_validation_debug (min)</x:v>
+      </x:c>
+      <x:c r="L1" s="14" t="str">
+        <x:v>First-pass Correct</x:v>
+      </x:c>
+      <x:c r="M1" s="14" t="str">
+        <x:v>Failure Attribution</x:v>
+      </x:c>
+      <x:c r="N1" s="14" t="str">
+        <x:v>Error Types</x:v>
+      </x:c>
+      <x:c r="O1" s="14" t="str">
+        <x:v>Knowledge Coverage Gap</x:v>
+      </x:c>
+      <x:c r="P1" s="14" t="str">
+        <x:v>Notes</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" ht="36" hidden="0" customHeight="1">
+      <x:c r="A2" s="18" t="str">
+        <x:v>2026-09-11</x:v>
+      </x:c>
+      <x:c r="B2" s="18" t="str">
+        <x:v>Foundation Check</x:v>
+      </x:c>
+      <x:c r="C2" s="18" t="str">
+        <x:v>FC-1 — even count + sum</x:v>
+      </x:c>
+      <x:c r="D2" s="18" t="str">
+        <x:v>C</x:v>
+      </x:c>
+      <x:c r="G2" s="18" t="str">
+        <x:v>CONDITIONAL PASS</x:v>
+      </x:c>
+      <x:c r="L2" s="18" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="M2" s="18" t="str">
+        <x:v>Correctness / Implementation</x:v>
+      </x:c>
+      <x:c r="N2" s="18" t="str">
+        <x:v>overflow; numeric type selection</x:v>
+      </x:c>
+      <x:c r="P2" s="18" t="str">
+        <x:v>Reported 6:58 after reading; not treated as valid T_solve. Core loop logic correct, but sum stored in int although worst-case sum is 1e14.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" ht="36" hidden="0" customHeight="1">
+      <x:c r="A3" s="18" t="str">
+        <x:v>2026-09-11</x:v>
+      </x:c>
+      <x:c r="B3" s="18" t="str">
+        <x:v>Foundation Check</x:v>
+      </x:c>
+      <x:c r="C3" s="18" t="str">
+        <x:v>FC-2 — nested loop complexity</x:v>
+      </x:c>
+      <x:c r="D3" s="18" t="str">
+        <x:v>C</x:v>
+      </x:c>
+      <x:c r="G3" s="18" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="L3" s="18" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="M3" s="18" t="str">
+        <x:v>N/A</x:v>
+      </x:c>
+      <x:c r="P3" s="18" t="str">
+        <x:v>Reported 3:48 after reading; not treated as valid T_solve. Correctly derived O(N log N).</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" ht="36" hidden="0" customHeight="1">
+      <x:c r="A4" s="18" t="str">
+        <x:v>2026-09-11</x:v>
+      </x:c>
+      <x:c r="B4" s="18" t="str">
+        <x:v>Foundation Check</x:v>
+      </x:c>
+      <x:c r="C4" s="18" t="str">
+        <x:v>FC-3 — multiplication overflow</x:v>
+      </x:c>
+      <x:c r="D4" s="18" t="str">
+        <x:v>C</x:v>
+      </x:c>
+      <x:c r="G4" s="18" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="L4" s="18" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="M4" s="18" t="str">
+        <x:v>N/A</x:v>
+      </x:c>
+      <x:c r="P4" s="18" t="str">
+        <x:v>Reported 2:18 after reading; not treated as valid T_solve. Correctly recognized int multiplication overflow risk and promoted operands to long long.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="36" hidden="0" customHeight="1">
+      <x:c r="A5" s="18" t="str">
+        <x:v>2026-09-11</x:v>
+      </x:c>
+      <x:c r="B5" s="18" t="str">
+        <x:v>Baseline Problem A</x:v>
+      </x:c>
+      <x:c r="C5" s="18" t="str">
+        <x:v>LeetCode 977 — Squares of a Sorted Array</x:v>
+      </x:c>
+      <x:c r="D5" s="18" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="E5" s="18" t="str">
+        <x:v>R1</x:v>
+      </x:c>
+      <x:c r="F5" s="18" t="str">
+        <x:v>I1</x:v>
+      </x:c>
+      <x:c r="G5" s="18" t="str">
+        <x:v>FAIL</x:v>
+      </x:c>
+      <x:c r="H5" s="18" t="n">
+        <x:v>12.033</x:v>
+      </x:c>
+      <x:c r="L5" s="18" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="M5" s="18" t="str">
+        <x:v>Implementation / Complexity</x:v>
+      </x:c>
+      <x:c r="N5" s="18" t="str">
+        <x:v>incomplete C++ implementation; sort complexity misanalysis</x:v>
+      </x:c>
+      <x:c r="O5" s="18" t="str">
+        <x:v>vector construction / STL syntax</x:v>
+      </x:c>
+      <x:c r="P5" s="18" t="str">
+        <x:v>Valid square-then-sort idea, but no compilable C++ vector implementation. Treated sort as O(N) instead of O(N log N).</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="36" hidden="0" customHeight="1">
+      <x:c r="A6" s="18" t="str">
+        <x:v>2026-09-11</x:v>
+      </x:c>
+      <x:c r="B6" s="18" t="str">
+        <x:v>Baseline Problem B</x:v>
+      </x:c>
+      <x:c r="C6" s="18" t="str">
+        <x:v>LeetCode 26 — Remove Duplicates from Sorted Array</x:v>
+      </x:c>
+      <x:c r="D6" s="18" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="E6" s="18" t="str">
+        <x:v>R2</x:v>
+      </x:c>
+      <x:c r="F6" s="18" t="str">
+        <x:v>I2</x:v>
+      </x:c>
+      <x:c r="G6" s="18" t="str">
+        <x:v>FAIL</x:v>
+      </x:c>
+      <x:c r="H6" s="18" t="n">
+        <x:v>12.383</x:v>
+      </x:c>
+      <x:c r="L6" s="18" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="M6" s="18" t="str">
+        <x:v>Correctness / Implementation</x:v>
+      </x:c>
+      <x:c r="N6" s="18" t="str">
+        <x:v>in-place contract violation; invalid vector construction</x:v>
+      </x:c>
+      <x:c r="O6" s="18" t="str">
+        <x:v>vector construction / in-place mutation</x:v>
+      </x:c>
+      <x:c r="P6" s="18" t="str">
+        <x:v>Recognized sorted-order duplicate handling, but created a separate result vector and never rewrote nums[0..k-1], violating the required output contract.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="36" hidden="0" customHeight="1">
+      <x:c r="A7" s="18" t="str">
+        <x:v>2026-09-11</x:v>
+      </x:c>
+      <x:c r="B7" s="18" t="str">
+        <x:v>Baseline Problem C</x:v>
+      </x:c>
+      <x:c r="C7" s="18" t="str">
+        <x:v>LeetCode 334 — Increasing Triplet Subsequence</x:v>
+      </x:c>
+      <x:c r="D7" s="18" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="E7" s="18" t="str">
+        <x:v>R3</x:v>
+      </x:c>
+      <x:c r="F7" s="18" t="str">
+        <x:v>I2</x:v>
+      </x:c>
+      <x:c r="G7" s="18" t="str">
+        <x:v>FAIL</x:v>
+      </x:c>
+      <x:c r="H7" s="18" t="n">
+        <x:v>112.183</x:v>
+      </x:c>
+      <x:c r="L7" s="18" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="M7" s="18" t="str">
+        <x:v>Correctness / Implementation</x:v>
+      </x:c>
+      <x:c r="N7" s="18" t="str">
+        <x:v>incorrect invariant; false positive; bitwise XOR used as exponent; invalid vector initialization; stale candidate variables</x:v>
+      </x:c>
+      <x:c r="O7" s="18" t="str">
+        <x:v>C++ vector initialization; operator semantics (^ is XOR, not exponentiation)</x:v>
+      </x:c>
+      <x:c r="P7" s="18" t="str">
+        <x:v>O(N) and O(1) complexity analysis matches intended state size, but the algorithm is structurally incorrect. Counterexample: [1,2,1,2] can trigger true although no strictly increasing triplet exists.</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="14" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="28" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="10" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="14" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="16" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="14" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="22" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="24" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="24" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="22" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="20" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="16" hidden="0" customWidth="1"/>
+    <x:col min="13" max="13" width="45" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1">
+      <x:c r="A1" s="14" t="str">
+        <x:v>Date</x:v>
+      </x:c>
+      <x:c r="B1" s="14" t="str">
+        <x:v>Target Test Profile</x:v>
+      </x:c>
+      <x:c r="C1" s="14" t="str">
+        <x:v>Formal?</x:v>
+      </x:c>
+      <x:c r="D1" s="14" t="str">
+        <x:v>Problem Count</x:v>
+      </x:c>
+      <x:c r="E1" s="14" t="str">
+        <x:v>Time Limit (min)</x:v>
+      </x:c>
+      <x:c r="F1" s="14" t="str">
+        <x:v>C++ Standard</x:v>
+      </x:c>
+      <x:c r="G1" s="14" t="str">
+        <x:v>Compiler / Execution</x:v>
+      </x:c>
+      <x:c r="H1" s="14" t="str">
+        <x:v>Documentation / Internet</x:v>
+      </x:c>
+      <x:c r="I1" s="14" t="str">
+        <x:v>Scoring / Pass Threshold</x:v>
+      </x:c>
+      <x:c r="J1" s="14" t="str">
+        <x:v>Format</x:v>
+      </x:c>
+      <x:c r="K1" s="14" t="str">
+        <x:v>Multiple Submissions</x:v>
+      </x:c>
+      <x:c r="L1" s="14" t="str">
+        <x:v>Result</x:v>
+      </x:c>
+      <x:c r="M1" s="14" t="str">
+        <x:v>Notes</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="28" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="24" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="18" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="45" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="45" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="45" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="14" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1">
+      <x:c r="A1" s="14" t="str">
+        <x:v>Target Test Profile</x:v>
+      </x:c>
+      <x:c r="B1" s="14" t="str">
+        <x:v>Axis</x:v>
+      </x:c>
+      <x:c r="C1" s="14" t="str">
+        <x:v>Status</x:v>
+      </x:c>
+      <x:c r="D1" s="14" t="str">
+        <x:v>Evidence</x:v>
+      </x:c>
+      <x:c r="E1" s="14" t="str">
+        <x:v>Blocking Gaps</x:v>
+      </x:c>
+      <x:c r="F1" s="14" t="str">
+        <x:v>Next Action</x:v>
+      </x:c>
+      <x:c r="G1" s="14" t="str">
+        <x:v>Last Updated</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="28" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="38" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="60" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="14" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="30" hidden="0" customHeight="1">
+      <x:c r="A1" s="14" t="str">
+        <x:v>CP Learning Dashboard</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" ht="30" hidden="0" customHeight="1">
+      <x:c r="A3" s="14" t="str">
+        <x:v>Metric</x:v>
+      </x:c>
+      <x:c r="B3" s="14" t="str">
+        <x:v>Current Value</x:v>
+      </x:c>
+      <x:c r="C3" s="14" t="str">
+        <x:v>Evidence / Note</x:v>
+      </x:c>
+      <x:c r="D3" s="14" t="str">
+        <x:v>Last Updated</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" ht="30" hidden="0" customHeight="1">
+      <x:c r="A4" s="18" t="str">
+        <x:v>Current Stage</x:v>
+      </x:c>
+      <x:c r="B4" s="18" t="str">
+        <x:v>Stage 0</x:v>
+      </x:c>
+      <x:c r="C4" s="18" t="str">
+        <x:v>S0-A in progress</x:v>
+      </x:c>
+      <x:c r="D4" s="18" t="str">
+        <x:v>2026-09-11</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="30" hidden="0" customHeight="1">
+      <x:c r="A5" s="18" t="str">
+        <x:v>Current Learning Unit</x:v>
+      </x:c>
+      <x:c r="B5" s="18" t="str">
+        <x:v>S0-A — C++ Basic Execution</x:v>
+      </x:c>
+      <x:c r="C5" s="18" t="str">
+        <x:v>Part E intermediate assessment PASS; proceed to Part F final assessment</x:v>
+      </x:c>
+      <x:c r="D5" s="18" t="str">
+        <x:v>2026-09-11</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="30" hidden="0" customHeight="1">
+      <x:c r="A6" s="18" t="str">
+        <x:v>Baseline independent range</x:v>
+      </x:c>
+      <x:c r="B6" s="18" t="str">
+        <x:v>R1/I1 reliable; R2 reasoning partial; R3 not yet solved</x:v>
+      </x:c>
+      <x:c r="C6" s="18" t="str">
+        <x:v>Approximate snapshot, not a fixed ceiling</x:v>
+      </x:c>
+      <x:c r="D6" s="18" t="str">
+        <x:v>2026-09-11</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="30" hidden="0" customHeight="1">
+      <x:c r="A7" s="18" t="str">
+        <x:v>Primary knowledge gap</x:v>
+      </x:c>
+      <x:c r="B7" s="18" t="str">
+        <x:v>vector/STL implementation</x:v>
+      </x:c>
+      <x:c r="C7" s="18" t="str">
+        <x:v>Observed in Baseline Problems A and B; addressed later in S0-B</x:v>
+      </x:c>
+      <x:c r="D7" s="18" t="str">
+        <x:v>2026-09-11</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="30" hidden="0" customHeight="1">
+      <x:c r="A8" s="18" t="str">
+        <x:v>Primary reasoning gap</x:v>
+      </x:c>
+      <x:c r="B8" s="18" t="str">
+        <x:v>correctness invariant / counterexample validation</x:v>
+      </x:c>
+      <x:c r="C8" s="18" t="str">
+        <x:v>Observed strongly in Baseline Problem C</x:v>
+      </x:c>
+      <x:c r="D8" s="18" t="str">
+        <x:v>2026-09-11</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="30" hidden="0" customHeight="1">
+      <x:c r="A9" s="18" t="str">
+        <x:v>Current S0-A diagnostic</x:v>
+      </x:c>
+      <x:c r="B9" s="18" t="str">
+        <x:v>Intermediate PASS — L3 Provisional</x:v>
+      </x:c>
+      <x:c r="C9" s="18" t="str">
+        <x:v>Clean retest passed in 4:40; edge-case self-check not explicitly listed</x:v>
+      </x:c>
+      <x:c r="D9" s="18" t="str">
+        <x:v>2026-09-11</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="30" hidden="0" customHeight="1">
+      <x:c r="A10" s="18" t="str">
+        <x:v>Review Debt</x:v>
+      </x:c>
+      <x:c r="B10" s="18" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="C10" s="18" t="str">
+        <x:v>No Review Debt; final assessment pending</x:v>
+      </x:c>
+      <x:c r="D10" s="18" t="str">
+        <x:v>2026-09-11</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:mergeCells>
+    <x:mergeCell ref="A1:D1"/>
+  </x:mergeCells>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
 </file>
--- a/records/CP_Learning_Record.xlsx
+++ b/records/CP_Learning_Record.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reference" sheetId="1" r:id="R6c939c68a10846e2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Assessments" sheetId="2" r:id="R864413c67c8c4c28"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mastery" sheetId="3" r:id="R1c4bc4eb7c2f4168"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decision_Coverage" sheetId="4" r:id="Re2dc3815f65d4c5a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Review_Debt" sheetId="5" r:id="R85a91cf5845541bd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Baseline" sheetId="6" r:id="Rf3945651fec74c83"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mocks" sheetId="7" r:id="R5e0dd23ce331468e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Readiness" sheetId="8" r:id="Rcb24622494c64e6a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="9" r:id="Re767854e900141e7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reference" sheetId="1" r:id="R64d610c9006a4d3b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Assessments" sheetId="2" r:id="Rd4ac0ac7f8a94731"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mastery" sheetId="3" r:id="R2e4b3d4a5fd642d7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decision_Coverage" sheetId="4" r:id="R6fe9475e86c04a26"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Review_Debt" sheetId="5" r:id="R2328eb3985e942e1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Baseline" sheetId="6" r:id="Rb69c87f518434876"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mocks" sheetId="7" r:id="Ra1d3b1592fbb4f4d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Readiness" sheetId="8" r:id="Rc400ed334d5947b6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="9" r:id="Rdd6433c599424e83"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -695,6 +695,92 @@
         <x:v>Clean independent retest. Submitted program compiles and is correct on the sample, boundary-oriented tests, and randomized differential checks. Required helper function is defined and called. O(N) time and O(1) extra-space explanations are correct. No edge case was explicitly listed, but the implementation handles key categories including x&lt;0, x=0, positive even/odd values, N=1, and input bounds; omission of an explicit self-check is retained as a process note rather than a correctness failure. Proceed to Part F final assessment.</x:v>
       </x:c>
     </x:row>
+    <x:row r="4">
+      <x:c r="A4" t="str">
+        <x:v>2026-09-11</x:v>
+      </x:c>
+      <x:c r="B4" t="str">
+        <x:v>S0-A — C++ Basic Execution</x:v>
+      </x:c>
+      <x:c r="C4" t="str">
+        <x:v>Final Assessment — Attempt 1</x:v>
+      </x:c>
+      <x:c r="D4" t="str">
+        <x:v>Longest contiguous nonzero sign-alternating segment</x:v>
+      </x:c>
+      <x:c r="E4" t="str">
+        <x:v>B</x:v>
+      </x:c>
+      <x:c r="F4" t="str">
+        <x:v>Reference execution + exhaustive small-case verification + randomized differential verification</x:v>
+      </x:c>
+      <x:c r="G4" t="str">
+        <x:v>R1</x:v>
+      </x:c>
+      <x:c r="H4" t="str">
+        <x:v>I2</x:v>
+      </x:c>
+      <x:c r="I4" t="str">
+        <x:v>Comparative / Provisional</x:v>
+      </x:c>
+      <x:c r="J4" t="str">
+        <x:v>CP_Calibration_Anchor_Registry_v1.1</x:v>
+      </x:c>
+      <x:c r="K4" t="str">
+        <x:v>Basic execution: input + conditional branching + loop + helper function + scalar state tracking</x:v>
+      </x:c>
+      <x:c r="L4" t="str">
+        <x:v>Incomplete</x:v>
+      </x:c>
+      <x:c r="M4" t="str">
+        <x:v>Immediate</x:v>
+      </x:c>
+      <x:c r="N4"/>
+      <x:c r="O4" t="n">
+        <x:v>28.716666666666665</x:v>
+      </x:c>
+      <x:c r="P4"/>
+      <x:c r="Q4"/>
+      <x:c r="R4"/>
+      <x:c r="S4"/>
+      <x:c r="T4"/>
+      <x:c r="U4" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="V4" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="W4" t="str">
+        <x:v>FAIL</x:v>
+      </x:c>
+      <x:c r="X4" t="str">
+        <x:v>Correctness</x:v>
+      </x:c>
+      <x:c r="Y4" t="str">
+        <x:v>Important zero-boundary handling failure; first zero counted as length 1; zero/nonzero transition unconditionally resets current length to 0; no edge-case self-check</x:v>
+      </x:c>
+      <x:c r="Z4" t="str">
+        <x:v>L3</x:v>
+      </x:c>
+      <x:c r="AA4" t="str">
+        <x:v>Provisional</x:v>
+      </x:c>
+      <x:c r="AB4" t="str">
+        <x:v>Immediate</x:v>
+      </x:c>
+      <x:c r="AC4" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="AD4" t="str">
+        <x:v>N/A</x:v>
+      </x:c>
+      <x:c r="AE4" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="AF4" t="str">
+        <x:v>Core O(N)/O(1) state-tracking idea is viable and sample/nonzero alternating cases work, but important zero cases fail. Counterexamples: N=1,[0] returns 1 instead of 0; [0,5,-3] returns 1 instead of 2. The duplicated unconditional `sum1 = 0;` inside the zero-product branch erases a valid new length-1 segment when previous value is zero and current value is nonzero. First-element logic also counts zero as a valid segment. First formal final-assessment FAIL; per v5.4 §39.1, convert this problem to learning mode, remediate, then reassess with a new equivalent problem.</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -784,7 +870,7 @@
         <x:v>Immediate</x:v>
       </x:c>
       <x:c r="G2" s="18" t="str">
-        <x:v>Sufficient for Provisional</x:v>
+        <x:v>Incomplete</x:v>
       </x:c>
       <x:c r="H2" s="18" t="str">
         <x:v>None</x:v>
@@ -793,19 +879,19 @@
         <x:v>N/A</x:v>
       </x:c>
       <x:c r="J2" s="18" t="str">
-        <x:v>No</x:v>
+        <x:v>Yes</x:v>
       </x:c>
       <x:c r="K2" s="18" t="str">
         <x:v>2026-09-11</x:v>
       </x:c>
       <x:c r="L2" t="str">
-        <x:v>Final Assessment</x:v>
+        <x:v>Final Assessment Retest after remediation</x:v>
       </x:c>
       <x:c r="M2" s="18" t="str">
-        <x:v>Explicit edge-case self-validation has not yet been demonstrated; final assessment is still required for S0-A completion.</x:v>
+        <x:v>Zero-boundary state handling and explicit edge-case self-validation.</x:v>
       </x:c>
       <x:c r="N2" s="18" t="str">
-        <x:v>Clean Part E retest PASS in 4:40. Correct input handling, branching, loop, helper function, scalar accumulation, and O(N)/O(1) analysis. Proceed to Part F.</x:v>
+        <x:v>Intermediate retest PASS in 4:40 established L3 evidence. Final Assessment Attempt 1 FAIL in 28:43 due important zero-case correctness errors. Keep L3/Provisional; remediate state-reset logic and edge-case validation, then use a new equivalent final-assessment problem.</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="42" hidden="0" customHeight="1">
@@ -1439,7 +1525,7 @@
         <x:v>S0-A — C++ Basic Execution</x:v>
       </x:c>
       <x:c r="C5" s="18" t="str">
-        <x:v>Part E intermediate assessment PASS; proceed to Part F final assessment</x:v>
+        <x:v>Part F final assessment attempt 1 FAIL; remediation + clean retest required</x:v>
       </x:c>
       <x:c r="D5" s="18" t="str">
         <x:v>2026-09-11</x:v>
@@ -1492,10 +1578,10 @@
         <x:v>Current S0-A diagnostic</x:v>
       </x:c>
       <x:c r="B9" s="18" t="str">
-        <x:v>Intermediate PASS — L3 Provisional</x:v>
+        <x:v>Final FAIL — L3 Provisional</x:v>
       </x:c>
       <x:c r="C9" s="18" t="str">
-        <x:v>Clean retest passed in 4:40; edge-case self-check not explicitly listed</x:v>
+        <x:v>Intermediate PASS retained; zero-boundary correctness failure in final assessment (28:43)</x:v>
       </x:c>
       <x:c r="D9" s="18" t="str">
         <x:v>2026-09-11</x:v>
@@ -1509,7 +1595,7 @@
         <x:v>None</x:v>
       </x:c>
       <x:c r="C10" s="18" t="str">
-        <x:v>No Review Debt; final assessment pending</x:v>
+        <x:v>No Review Debt yet; immediate final-assessment retest pending after remediation</x:v>
       </x:c>
       <x:c r="D10" s="18" t="str">
         <x:v>2026-09-11</x:v>

--- a/records/CP_Learning_Record.xlsx
+++ b/records/CP_Learning_Record.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reference" sheetId="1" r:id="R64d610c9006a4d3b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Assessments" sheetId="2" r:id="Rd4ac0ac7f8a94731"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mastery" sheetId="3" r:id="R2e4b3d4a5fd642d7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decision_Coverage" sheetId="4" r:id="R6fe9475e86c04a26"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Review_Debt" sheetId="5" r:id="R2328eb3985e942e1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Baseline" sheetId="6" r:id="Rb69c87f518434876"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mocks" sheetId="7" r:id="Ra1d3b1592fbb4f4d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Readiness" sheetId="8" r:id="Rc400ed334d5947b6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="9" r:id="Rdd6433c599424e83"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reference" sheetId="1" r:id="Rd0179b8647ba48f1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Assessments" sheetId="2" r:id="R3a83d6784f264234"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mastery" sheetId="3" r:id="Rd73a6ea8f3e94a0e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decision_Coverage" sheetId="4" r:id="R3c91d9d715694ea4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Review_Debt" sheetId="5" r:id="R4a93883ed54f4c59"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Baseline" sheetId="6" r:id="Rab531c4d4dba44f7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mocks" sheetId="7" r:id="R2f3602a6d70b46f5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Readiness" sheetId="8" r:id="Rdc71d123b31c4228"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="9" r:id="Rb9e64f68e367494f"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -781,6 +781,92 @@
         <x:v>Core O(N)/O(1) state-tracking idea is viable and sample/nonzero alternating cases work, but important zero cases fail. Counterexamples: N=1,[0] returns 1 instead of 0; [0,5,-3] returns 1 instead of 2. The duplicated unconditional `sum1 = 0;` inside the zero-product branch erases a valid new length-1 segment when previous value is zero and current value is nonzero. First-element logic also counts zero as a valid segment. First formal final-assessment FAIL; per v5.4 §39.1, convert this problem to learning mode, remediate, then reassess with a new equivalent problem.</x:v>
       </x:c>
     </x:row>
+    <x:row r="5">
+      <x:c r="A5" t="str">
+        <x:v>2026-09-11</x:v>
+      </x:c>
+      <x:c r="B5" t="str">
+        <x:v>S0-A — C++ Basic Execution</x:v>
+      </x:c>
+      <x:c r="C5" t="str">
+        <x:v>Final Assessment — Retest 1</x:v>
+      </x:c>
+      <x:c r="D5" t="str">
+        <x:v>Balance recovery count and maximum post-transaction balance</x:v>
+      </x:c>
+      <x:c r="E5" t="str">
+        <x:v>B</x:v>
+      </x:c>
+      <x:c r="F5" t="str">
+        <x:v>Reference execution + exhaustive small-case verification + randomized differential verification</x:v>
+      </x:c>
+      <x:c r="G5" t="str">
+        <x:v>R1</x:v>
+      </x:c>
+      <x:c r="H5" t="str">
+        <x:v>I2</x:v>
+      </x:c>
+      <x:c r="I5" t="str">
+        <x:v>Comparative / Provisional</x:v>
+      </x:c>
+      <x:c r="J5" t="str">
+        <x:v>CP_Calibration_Anchor_Registry_v1.1</x:v>
+      </x:c>
+      <x:c r="K5" t="str">
+        <x:v>Basic execution: input + conditional branching + loop + helper function + scalar state tracking + initial-state handling</x:v>
+      </x:c>
+      <x:c r="L5" t="str">
+        <x:v>Incomplete</x:v>
+      </x:c>
+      <x:c r="M5" t="str">
+        <x:v>Immediate</x:v>
+      </x:c>
+      <x:c r="N5"/>
+      <x:c r="O5" t="n">
+        <x:v>15.1</x:v>
+      </x:c>
+      <x:c r="P5"/>
+      <x:c r="Q5"/>
+      <x:c r="R5"/>
+      <x:c r="S5"/>
+      <x:c r="T5"/>
+      <x:c r="U5" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="V5" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="W5" t="str">
+        <x:v>FAIL</x:v>
+      </x:c>
+      <x:c r="X5" t="str">
+        <x:v>Correctness</x:v>
+      </x:c>
+      <x:c r="Y5" t="str">
+        <x:v>Initial-state transition omitted: first transaction from balance 0 to positive is a recovery; no edge-case self-check; repeated boundary/initialization validation failure</x:v>
+      </x:c>
+      <x:c r="Z5" t="str">
+        <x:v>L3</x:v>
+      </x:c>
+      <x:c r="AA5" t="str">
+        <x:v>Provisional</x:v>
+      </x:c>
+      <x:c r="AB5" t="str">
+        <x:v>Immediate</x:v>
+      </x:c>
+      <x:c r="AC5" t="str">
+        <x:v>Open</x:v>
+      </x:c>
+      <x:c r="AD5" t="str">
+        <x:v>Medium</x:v>
+      </x:c>
+      <x:c r="AE5" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="AF5" t="str">
+        <x:v>Core O(N)/O(1) design and maximum-balance tracking are sound, but the special-case first iteration skips recovery detection. Counterexample: N=1, x=5 should output `1 5`, but submitted code outputs `0 5`. This is the second consecutive skill-related final-assessment FAIL on the same Learning Objective, with repeated boundary/edge-case validation weakness. Per v5.4 §39.2, pause formal retesting and perform diagnostic remediation before another new formal final-assessment problem.</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -873,10 +959,10 @@
         <x:v>Incomplete</x:v>
       </x:c>
       <x:c r="H2" s="18" t="str">
-        <x:v>None</x:v>
+        <x:v>Open</x:v>
       </x:c>
       <x:c r="I2" s="18" t="str">
-        <x:v>N/A</x:v>
+        <x:v>Medium</x:v>
       </x:c>
       <x:c r="J2" s="18" t="str">
         <x:v>Yes</x:v>
@@ -885,13 +971,13 @@
         <x:v>2026-09-11</x:v>
       </x:c>
       <x:c r="L2" t="str">
-        <x:v>Final Assessment Retest after remediation</x:v>
+        <x:v>Diagnostic remediation checkpoint before next Final Assessment</x:v>
       </x:c>
       <x:c r="M2" s="18" t="str">
-        <x:v>Zero-boundary state handling and explicit edge-case self-validation.</x:v>
+        <x:v>Repeated boundary/initial-state handling errors and absent explicit edge-case self-validation.</x:v>
       </x:c>
       <x:c r="N2" s="18" t="str">
-        <x:v>Intermediate retest PASS in 4:40 established L3 evidence. Final Assessment Attempt 1 FAIL in 28:43 due important zero-case correctness errors. Keep L3/Provisional; remediate state-reset logic and edge-case validation, then use a new equivalent final-assessment problem.</x:v>
+        <x:v>Intermediate retest PASS (4:40) still supports L3 implementation capability, but two consecutive skill-related final-assessment FAILs occurred (28:43, 15:06). Per v5.4 §39.2, stop simple retesting and perform diagnostic remediation. Medium Review Debt opened because the same boundary/edge-case validation error pattern repeated.</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="42" hidden="0" customHeight="1">
@@ -1080,6 +1166,39 @@
       </x:c>
       <x:c r="K1" s="14" t="str">
         <x:v>Notes</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" t="str">
+        <x:v>2026-09-11</x:v>
+      </x:c>
+      <x:c r="B2" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C2" t="str">
+        <x:v>S0-A — C++ Basic Execution</x:v>
+      </x:c>
+      <x:c r="D2" t="str">
+        <x:v>Medium</x:v>
+      </x:c>
+      <x:c r="E2" t="str">
+        <x:v>Repeated boundary/initial-state correctness errors and no explicit edge-case self-validation across two consecutive final assessments.</x:v>
+      </x:c>
+      <x:c r="F2" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="G2" t="str">
+        <x:v>Open</x:v>
+      </x:c>
+      <x:c r="H2" t="str">
+        <x:v>Diagnostic remediation: isolate initialization/first-step transitions, define state variables in words, and validate minimum/boundary cases before code lock; pass remediation checkpoint before new formal final-assessment retest.</x:v>
+      </x:c>
+      <x:c r="I2" t="str">
+        <x:v>Before next S0-A Final Assessment</x:v>
+      </x:c>
+      <x:c r="J2"/>
+      <x:c r="K2" t="str">
+        <x:v>Opened under v5.4 §28.3 because the same error type repeated. This is not a retroactive cancellation of the earlier intermediate PASS; S0-A remains incomplete.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -1525,7 +1644,7 @@
         <x:v>S0-A — C++ Basic Execution</x:v>
       </x:c>
       <x:c r="C5" s="18" t="str">
-        <x:v>Part F final assessment attempt 1 FAIL; remediation + clean retest required</x:v>
+        <x:v>Two consecutive Part F FAILs; diagnostic remediation required before another formal retest</x:v>
       </x:c>
       <x:c r="D5" s="18" t="str">
         <x:v>2026-09-11</x:v>
@@ -1564,10 +1683,10 @@
         <x:v>Primary reasoning gap</x:v>
       </x:c>
       <x:c r="B8" s="18" t="str">
-        <x:v>correctness invariant / counterexample validation</x:v>
+        <x:v>boundary / initial-state correctness + counterexample validation</x:v>
       </x:c>
       <x:c r="C8" s="18" t="str">
-        <x:v>Observed strongly in Baseline Problem C</x:v>
+        <x:v>Repeated in two consecutive S0-A final assessments</x:v>
       </x:c>
       <x:c r="D8" s="18" t="str">
         <x:v>2026-09-11</x:v>
@@ -1578,10 +1697,10 @@
         <x:v>Current S0-A diagnostic</x:v>
       </x:c>
       <x:c r="B9" s="18" t="str">
-        <x:v>Final FAIL — L3 Provisional</x:v>
+        <x:v>Final Retest 1 FAIL — L3 Provisional</x:v>
       </x:c>
       <x:c r="C9" s="18" t="str">
-        <x:v>Intermediate PASS retained; zero-boundary correctness failure in final assessment (28:43)</x:v>
+        <x:v>First-transaction recovery omitted; T_solve 15:06; §39.2 remediation escalation active</x:v>
       </x:c>
       <x:c r="D9" s="18" t="str">
         <x:v>2026-09-11</x:v>
@@ -1592,10 +1711,10 @@
         <x:v>Review Debt</x:v>
       </x:c>
       <x:c r="B10" s="18" t="str">
-        <x:v>None</x:v>
+        <x:v>1 Open (Medium)</x:v>
       </x:c>
       <x:c r="C10" s="18" t="str">
-        <x:v>No Review Debt yet; immediate final-assessment retest pending after remediation</x:v>
+        <x:v>Repeated boundary/edge-case validation weakness in S0-A; prerequisite-blocking until remediation checkpoint</x:v>
       </x:c>
       <x:c r="D10" s="18" t="str">
         <x:v>2026-09-11</x:v>

--- a/records/CP_Learning_Record.xlsx
+++ b/records/CP_Learning_Record.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reference" sheetId="1" r:id="Rd0179b8647ba48f1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Assessments" sheetId="2" r:id="R3a83d6784f264234"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mastery" sheetId="3" r:id="Rd73a6ea8f3e94a0e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decision_Coverage" sheetId="4" r:id="R3c91d9d715694ea4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Review_Debt" sheetId="5" r:id="R4a93883ed54f4c59"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Baseline" sheetId="6" r:id="Rab531c4d4dba44f7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mocks" sheetId="7" r:id="R2f3602a6d70b46f5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Readiness" sheetId="8" r:id="Rdc71d123b31c4228"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="9" r:id="Rb9e64f68e367494f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reference" sheetId="1" r:id="Rabd7a892e94a48fe"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Assessments" sheetId="2" r:id="R4355f10e95614807"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mastery" sheetId="3" r:id="R981911e19bea488c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decision_Coverage" sheetId="4" r:id="R81504c1e4f904687"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Review_Debt" sheetId="5" r:id="R377592fb091f4e59"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Baseline" sheetId="6" r:id="R1114d8f0c5824eb6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mocks" sheetId="7" r:id="Rf06ef37e01f347c7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Readiness" sheetId="8" r:id="Rc1fd5d97902942ba"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="9" r:id="R44d5be2fedf44670"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -867,6 +867,92 @@
         <x:v>Core O(N)/O(1) design and maximum-balance tracking are sound, but the special-case first iteration skips recovery detection. Counterexample: N=1, x=5 should output `1 5`, but submitted code outputs `0 5`. This is the second consecutive skill-related final-assessment FAIL on the same Learning Objective, with repeated boundary/edge-case validation weakness. Per v5.4 §39.2, pause formal retesting and perform diagnostic remediation before another new formal final-assessment problem.</x:v>
       </x:c>
     </x:row>
+    <x:row r="6">
+      <x:c r="A6" t="str">
+        <x:v>2026-09-11</x:v>
+      </x:c>
+      <x:c r="B6" t="str">
+        <x:v>S0-A — C++ Basic Execution</x:v>
+      </x:c>
+      <x:c r="C6" t="str">
+        <x:v>Final Assessment — Retest 2</x:v>
+      </x:c>
+      <x:c r="D6" t="str">
+        <x:v>Record-break count and longest contiguous increasing segment</x:v>
+      </x:c>
+      <x:c r="E6" t="str">
+        <x:v>B</x:v>
+      </x:c>
+      <x:c r="F6" t="str">
+        <x:v>Exact-code compilation + sample/boundary execution + exhaustive small-case differential verification</x:v>
+      </x:c>
+      <x:c r="G6" t="str">
+        <x:v>R1</x:v>
+      </x:c>
+      <x:c r="H6" t="str">
+        <x:v>I2</x:v>
+      </x:c>
+      <x:c r="I6" t="str">
+        <x:v>Comparative / Provisional</x:v>
+      </x:c>
+      <x:c r="J6" t="str">
+        <x:v>CP_Calibration_Anchor_Registry_v1.1</x:v>
+      </x:c>
+      <x:c r="K6" t="str">
+        <x:v>Basic execution: input + conditional branching + loop + helper function + scalar state tracking + initialization/boundary handling</x:v>
+      </x:c>
+      <x:c r="L6" t="str">
+        <x:v>Sufficient for Provisional</x:v>
+      </x:c>
+      <x:c r="M6" t="str">
+        <x:v>Immediate; Compiler/Debugger allowed</x:v>
+      </x:c>
+      <x:c r="N6"/>
+      <x:c r="O6" t="n">
+        <x:v>33.06666666666667</x:v>
+      </x:c>
+      <x:c r="P6"/>
+      <x:c r="Q6"/>
+      <x:c r="R6"/>
+      <x:c r="S6"/>
+      <x:c r="T6"/>
+      <x:c r="U6" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="V6" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="W6" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="X6" t="str">
+        <x:v>N/A</x:v>
+      </x:c>
+      <x:c r="Y6" t="str">
+        <x:v>No correctness error. Learner explicitly self-checked N=1 =&gt; 1 1. VS debugger use was permitted but actual use was not reported.</x:v>
+      </x:c>
+      <x:c r="Z6" t="str">
+        <x:v>L3</x:v>
+      </x:c>
+      <x:c r="AA6" t="str">
+        <x:v>Provisional</x:v>
+      </x:c>
+      <x:c r="AB6" t="str">
+        <x:v>Immediate; Compiler/Debugger allowed</x:v>
+      </x:c>
+      <x:c r="AC6" t="str">
+        <x:v>Resolved</x:v>
+      </x:c>
+      <x:c r="AD6" t="str">
+        <x:v>N/A</x:v>
+      </x:c>
+      <x:c r="AE6" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="AF6" t="str">
+        <x:v>Clean independent final retest after diagnostic remediation. Exact code compiled under C++17 and matched the sample, boundary executions, and exhaustive small-case differential checks. Record-break logic is correct because a new record is necessarily greater than the immediately previous value, so incrementing the current increasing-run length in that branch is valid. O(N) time and O(1) extra-space analyses are correct. Repeated initial/boundary-state weakness is considered remediated at immediate-evidence level; proceed to mandatory Part G Adaptive Extra Problem.</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -956,28 +1042,28 @@
         <x:v>Immediate</x:v>
       </x:c>
       <x:c r="G2" s="18" t="str">
-        <x:v>Incomplete</x:v>
+        <x:v>Sufficient for Provisional</x:v>
       </x:c>
       <x:c r="H2" s="18" t="str">
-        <x:v>Open</x:v>
+        <x:v>Resolved</x:v>
       </x:c>
       <x:c r="I2" s="18" t="str">
-        <x:v>Medium</x:v>
+        <x:v>N/A</x:v>
       </x:c>
       <x:c r="J2" s="18" t="str">
-        <x:v>Yes</x:v>
+        <x:v>No</x:v>
       </x:c>
       <x:c r="K2" s="18" t="str">
         <x:v>2026-09-11</x:v>
       </x:c>
       <x:c r="L2" t="str">
-        <x:v>Diagnostic remediation checkpoint before next Final Assessment</x:v>
+        <x:v>Part G Adaptive Extra Problem</x:v>
       </x:c>
       <x:c r="M2" s="18" t="str">
-        <x:v>Repeated boundary/initial-state handling errors and absent explicit edge-case self-validation.</x:v>
+        <x:v>No blocking correctness issue remains in immediate evidence; continue explicit edge-case validation habit.</x:v>
       </x:c>
       <x:c r="N2" s="18" t="str">
-        <x:v>Intermediate retest PASS (4:40) still supports L3 implementation capability, but two consecutive skill-related final-assessment FAILs occurred (28:43, 15:06). Per v5.4 §39.2, stop simple retesting and perform diagnostic remediation. Medium Review Debt opened because the same boundary/edge-case validation error pattern repeated.</x:v>
+        <x:v>Intermediate retest PASS and Final Retest 2 PASS. Diagnostic remediation checkpoint correctly articulated state meanings and first-transition handling. Medium Review Debt from repeated boundary/initial-state errors resolved after clean final retest. Long-term confidence remains Provisional pending delayed/mixed evidence.</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="42" hidden="0" customHeight="1">
@@ -1188,17 +1274,19 @@
         <x:v>Yes</x:v>
       </x:c>
       <x:c r="G2" t="str">
-        <x:v>Open</x:v>
+        <x:v>Resolved</x:v>
       </x:c>
       <x:c r="H2" t="str">
-        <x:v>Diagnostic remediation: isolate initialization/first-step transitions, define state variables in words, and validate minimum/boundary cases before code lock; pass remediation checkpoint before new formal final-assessment retest.</x:v>
+        <x:v>Maintain mandatory explicit minimum/boundary-case self-check in future assessments; watch for recurrence in delayed/mixed evidence.</x:v>
       </x:c>
       <x:c r="I2" t="str">
-        <x:v>Before next S0-A Final Assessment</x:v>
-      </x:c>
-      <x:c r="J2"/>
+        <x:v>Delayed/Mixed Assessment</x:v>
+      </x:c>
+      <x:c r="J2" t="str">
+        <x:v>2026-09-11</x:v>
+      </x:c>
       <x:c r="K2" t="str">
-        <x:v>Opened under v5.4 §28.3 because the same error type repeated. This is not a retroactive cancellation of the earlier intermediate PASS; S0-A remains incomplete.</x:v>
+        <x:v>Diagnostic remediation checkpoint passed; subsequent Final Assessment Retest 2 passed independently with explicit N=1 edge-case check. Debt resolved, but recurrence should reopen debt.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -1630,7 +1718,7 @@
         <x:v>Stage 0</x:v>
       </x:c>
       <x:c r="C4" s="18" t="str">
-        <x:v>S0-A in progress</x:v>
+        <x:v>S0-A Part F passed; Part G next</x:v>
       </x:c>
       <x:c r="D4" s="18" t="str">
         <x:v>2026-09-11</x:v>
@@ -1644,7 +1732,7 @@
         <x:v>S0-A — C++ Basic Execution</x:v>
       </x:c>
       <x:c r="C5" s="18" t="str">
-        <x:v>Two consecutive Part F FAILs; diagnostic remediation required before another formal retest</x:v>
+        <x:v>Part E PASS + Part F PASS; mandatory Adaptive Extra Problem pending</x:v>
       </x:c>
       <x:c r="D5" s="18" t="str">
         <x:v>2026-09-11</x:v>
@@ -1686,7 +1774,7 @@
         <x:v>boundary / initial-state correctness + counterexample validation</x:v>
       </x:c>
       <x:c r="C8" s="18" t="str">
-        <x:v>Repeated in two consecutive S0-A final assessments</x:v>
+        <x:v>Immediate remediation succeeded; monitor for recurrence in delayed/mixed evidence</x:v>
       </x:c>
       <x:c r="D8" s="18" t="str">
         <x:v>2026-09-11</x:v>
@@ -1697,10 +1785,10 @@
         <x:v>Current S0-A diagnostic</x:v>
       </x:c>
       <x:c r="B9" s="18" t="str">
-        <x:v>Final Retest 1 FAIL — L3 Provisional</x:v>
+        <x:v>Final Retest 2 PASS — L3 Provisional</x:v>
       </x:c>
       <x:c r="C9" s="18" t="str">
-        <x:v>First-transaction recovery omitted; T_solve 15:06; §39.2 remediation escalation active</x:v>
+        <x:v>T_solve 33:04; explicit N=1 edge-case check; proceed to Part G</x:v>
       </x:c>
       <x:c r="D9" s="18" t="str">
         <x:v>2026-09-11</x:v>
@@ -1711,10 +1799,10 @@
         <x:v>Review Debt</x:v>
       </x:c>
       <x:c r="B10" s="18" t="str">
-        <x:v>1 Open (Medium)</x:v>
+        <x:v>0 Open</x:v>
       </x:c>
       <x:c r="C10" s="18" t="str">
-        <x:v>Repeated boundary/edge-case validation weakness in S0-A; prerequisite-blocking until remediation checkpoint</x:v>
+        <x:v>Prior Medium S0-A boundary/edge-case debt resolved after remediation + clean final retest</x:v>
       </x:c>
       <x:c r="D10" s="18" t="str">
         <x:v>2026-09-11</x:v>

--- a/records/CP_Learning_Record.xlsx
+++ b/records/CP_Learning_Record.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reference" sheetId="1" r:id="Rabd7a892e94a48fe"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Assessments" sheetId="2" r:id="R4355f10e95614807"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mastery" sheetId="3" r:id="R981911e19bea488c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decision_Coverage" sheetId="4" r:id="R81504c1e4f904687"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Review_Debt" sheetId="5" r:id="R377592fb091f4e59"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Baseline" sheetId="6" r:id="R1114d8f0c5824eb6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mocks" sheetId="7" r:id="Rf06ef37e01f347c7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Readiness" sheetId="8" r:id="Rc1fd5d97902942ba"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="9" r:id="R44d5be2fedf44670"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reference" sheetId="1" r:id="R8ad13d86ec39459a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Assessments" sheetId="2" r:id="R7eeb04ecba7d4d5d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mastery" sheetId="3" r:id="Rc7eb261593a148e1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decision_Coverage" sheetId="4" r:id="Rccbb99da83d04601"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Review_Debt" sheetId="5" r:id="Rc0e039fe131947f5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Baseline" sheetId="6" r:id="R3f032ec8ed70490a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mocks" sheetId="7" r:id="R41c476ae61a94407"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Readiness" sheetId="8" r:id="R86ef23a71c7e4797"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="9" r:id="Rf2f0dd9dc43149fe"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -21,87 +21,28 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:fonts count="2">
+  <x:fonts count="1">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
     </x:font>
-    <x:font>
-      <x:b/>
-      <x:sz val="11"/>
-      <x:color rgb="FFFFFFFF"/>
-      <x:name val="Carlito"/>
-    </x:font>
   </x:fonts>
-  <x:fills count="3">
+  <x:fills count="2">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
     <x:fill>
       <x:patternFill patternType="gray125"/>
     </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor rgb="FF1F4E78"/>
-      </x:patternFill>
-    </x:fill>
   </x:fills>
-  <x:borders count="2">
-    <x:border/>
+  <x:borders count="1">
     <x:border/>
   </x:borders>
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="20">
+  <x:cellXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="top"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="top"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="top" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="top" wrapText="1"/>
-    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -303,89 +244,61 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
-  <x:cols>
-    <x:col min="1" max="1" width="24" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="52" hidden="0" customWidth="1"/>
-  </x:cols>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" s="14" t="str">
+      <x:c r="A1" t="str">
         <x:v>Field</x:v>
       </x:c>
-      <x:c r="B1" s="14" t="str">
-        <x:v>Allowed / Meaning</x:v>
+      <x:c r="B1" t="str">
+        <x:v>Definition</x:v>
       </x:c>
     </x:row>
     <x:row r="2">
-      <x:c r="A2" s="15" t="str">
+      <x:c r="A2" t="str">
+        <x:v>Capability</x:v>
+      </x:c>
+      <x:c r="B2" t="str">
+        <x:v>L0-L5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" t="str">
+        <x:v>Confidence</x:v>
+      </x:c>
+      <x:c r="B3" t="str">
+        <x:v>Unverified / Provisional / Confirmed / Stable</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" t="str">
+        <x:v>Evidence Context</x:v>
+      </x:c>
+      <x:c r="B4" t="str">
+        <x:v>Baseline / Immediate / Delayed / Mixed / Timed</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" t="str">
         <x:v>Result</x:v>
       </x:c>
-      <x:c r="B2" s="15" t="str">
-        <x:v>PASS | CONDITIONAL PASS | FAIL | VOID</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="3">
-      <x:c r="A3" s="15" t="str">
-        <x:v>Validation Tier</x:v>
-      </x:c>
-      <x:c r="B3" s="15" t="str">
-        <x:v>A | B | C</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4">
-      <x:c r="A4" s="15" t="str">
-        <x:v>Capability</x:v>
-      </x:c>
-      <x:c r="B4" s="15" t="str">
-        <x:v>L0 | L1 | L2 | L3 | L4 | L5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5">
-      <x:c r="A5" s="15" t="str">
-        <x:v>Confidence</x:v>
-      </x:c>
-      <x:c r="B5" s="15" t="str">
-        <x:v>Unverified | Provisional | Confirmed | Stable</x:v>
+      <x:c r="B5" t="str">
+        <x:v>PASS / CONDITIONAL PASS / FAIL / VOID</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
-      <x:c r="A6" s="15" t="str">
-        <x:v>Review Debt</x:v>
-      </x:c>
-      <x:c r="B6" s="15" t="str">
-        <x:v>None | Open | Resolved</x:v>
+      <x:c r="A6" t="str">
+        <x:v>R/I</x:v>
+      </x:c>
+      <x:c r="B6" t="str">
+        <x:v>Recognition-Transfer / Implementation difficulty</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
-      <x:c r="A7" s="15" t="str">
-        <x:v>Review Debt Severity</x:v>
-      </x:c>
-      <x:c r="B7" s="15" t="str">
-        <x:v>N/A | Low | Medium | High</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8">
-      <x:c r="A8" s="15" t="str">
-        <x:v>First-pass Correct</x:v>
-      </x:c>
-      <x:c r="B8" s="15" t="str">
-        <x:v>Yes | No | N/A</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9">
-      <x:c r="A9" s="15" t="str">
-        <x:v>Hints</x:v>
-      </x:c>
-      <x:c r="B9" s="15" t="str">
-        <x:v>None | Requested | GPT-provided</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10">
-      <x:c r="A10" s="15" t="str">
-        <x:v>Formal?</x:v>
-      </x:c>
-      <x:c r="B10" s="15" t="str">
-        <x:v>Yes | No</x:v>
+      <x:c r="A7" t="str">
+        <x:v>Policy</x:v>
+      </x:c>
+      <x:c r="B7" t="str">
+        <x:v>v5.4 + CP_Calibration_Anchor_Registry_v1.1</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -396,217 +309,189 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
-  <x:cols>
-    <x:col min="1" max="1" width="12" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="18" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="30" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="12" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="20" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="8" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="8" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="14" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="25" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="28" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="22" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="20" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="14" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="14" hidden="0" customWidth="1"/>
-    <x:col min="16" max="16" width="16" hidden="0" customWidth="1"/>
-    <x:col min="17" max="17" width="16" hidden="0" customWidth="1"/>
-    <x:col min="18" max="18" width="18" hidden="0" customWidth="1"/>
-    <x:col min="19" max="19" width="14" hidden="0" customWidth="1"/>
-    <x:col min="20" max="20" width="16" hidden="0" customWidth="1"/>
-    <x:col min="21" max="21" width="16" hidden="0" customWidth="1"/>
-    <x:col min="22" max="22" width="14" hidden="0" customWidth="1"/>
-    <x:col min="23" max="23" width="16" hidden="0" customWidth="1"/>
-    <x:col min="24" max="24" width="22" hidden="0" customWidth="1"/>
-    <x:col min="25" max="25" width="30" hidden="0" customWidth="1"/>
-    <x:col min="26" max="26" width="16" hidden="0" customWidth="1"/>
-    <x:col min="27" max="27" width="18" hidden="0" customWidth="1"/>
-    <x:col min="28" max="28" width="20" hidden="0" customWidth="1"/>
-    <x:col min="29" max="29" width="14" hidden="0" customWidth="1"/>
-    <x:col min="30" max="30" width="18" hidden="0" customWidth="1"/>
-    <x:col min="31" max="31" width="16" hidden="0" customWidth="1"/>
-    <x:col min="32" max="32" width="45" hidden="0" customWidth="1"/>
-  </x:cols>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" s="14" t="str">
+      <x:c r="A1" t="str">
         <x:v>Date</x:v>
       </x:c>
-      <x:c r="B1" s="14" t="str">
+      <x:c r="B1" t="str">
         <x:v>Learning Unit</x:v>
       </x:c>
-      <x:c r="C1" s="14" t="str">
+      <x:c r="C1" t="str">
         <x:v>Assessment Type</x:v>
       </x:c>
-      <x:c r="D1" s="14" t="str">
+      <x:c r="D1" t="str">
         <x:v>Problem</x:v>
       </x:c>
-      <x:c r="E1" s="14" t="str">
+      <x:c r="E1" t="str">
         <x:v>Validation Tier</x:v>
       </x:c>
-      <x:c r="F1" s="14" t="str">
+      <x:c r="F1" t="str">
         <x:v>Validation Evidence</x:v>
       </x:c>
-      <x:c r="G1" s="14" t="str">
+      <x:c r="G1" t="str">
         <x:v>R</x:v>
       </x:c>
-      <x:c r="H1" s="14" t="str">
+      <x:c r="H1" t="str">
         <x:v>I</x:v>
       </x:c>
-      <x:c r="I1" s="14" t="str">
+      <x:c r="I1" t="str">
         <x:v>Calibration</x:v>
       </x:c>
-      <x:c r="J1" s="14" t="str">
+      <x:c r="J1" t="str">
         <x:v>Calibration Registry</x:v>
       </x:c>
-      <x:c r="K1" s="14" t="str">
+      <x:c r="K1" t="str">
         <x:v>Core Decision Boundary Coverage</x:v>
       </x:c>
-      <x:c r="L1" s="14" t="str">
+      <x:c r="L1" t="str">
         <x:v>Unit Coverage Status</x:v>
       </x:c>
-      <x:c r="M1" s="14" t="str">
+      <x:c r="M1" t="str">
         <x:v>Mode</x:v>
       </x:c>
-      <x:c r="N1" s="14" t="str">
+      <x:c r="N1" t="str">
         <x:v>Time Limit (min)</x:v>
       </x:c>
-      <x:c r="O1" s="14" t="str">
+      <x:c r="O1" t="str">
         <x:v>T_solve (min)</x:v>
       </x:c>
-      <x:c r="P1" s="14" t="str">
+      <x:c r="P1" t="str">
         <x:v>T_recognition (min)</x:v>
       </x:c>
-      <x:c r="Q1" s="14" t="str">
+      <x:c r="Q1" t="str">
         <x:v>T_implementation (min)</x:v>
       </x:c>
-      <x:c r="R1" s="14" t="str">
+      <x:c r="R1" t="str">
         <x:v>T_validation_debug (min)</x:v>
       </x:c>
-      <x:c r="S1" s="14" t="str">
+      <x:c r="S1" t="str">
         <x:v>T_explain (min)</x:v>
       </x:c>
-      <x:c r="T1" s="14" t="str">
+      <x:c r="T1" t="str">
         <x:v>Compile/Run/Submit Count</x:v>
       </x:c>
-      <x:c r="U1" s="14" t="str">
+      <x:c r="U1" t="str">
         <x:v>First-pass Correct</x:v>
       </x:c>
-      <x:c r="V1" s="14" t="str">
+      <x:c r="V1" t="str">
         <x:v>Hints</x:v>
       </x:c>
-      <x:c r="W1" s="14" t="str">
+      <x:c r="W1" t="str">
         <x:v>Result</x:v>
       </x:c>
-      <x:c r="X1" s="14" t="str">
+      <x:c r="X1" t="str">
         <x:v>Failure Attribution</x:v>
       </x:c>
-      <x:c r="Y1" s="14" t="str">
+      <x:c r="Y1" t="str">
         <x:v>Error Types</x:v>
       </x:c>
-      <x:c r="Z1" s="14" t="str">
+      <x:c r="Z1" t="str">
         <x:v>Capability Level</x:v>
       </x:c>
-      <x:c r="AA1" s="14" t="str">
+      <x:c r="AA1" t="str">
         <x:v>Confidence Status</x:v>
       </x:c>
-      <x:c r="AB1" s="14" t="str">
+      <x:c r="AB1" t="str">
         <x:v>Evidence Context</x:v>
       </x:c>
-      <x:c r="AC1" s="14" t="str">
+      <x:c r="AC1" t="str">
         <x:v>Review Debt</x:v>
       </x:c>
-      <x:c r="AD1" s="14" t="str">
+      <x:c r="AD1" t="str">
         <x:v>Review Debt Severity</x:v>
       </x:c>
-      <x:c r="AE1" s="14" t="str">
+      <x:c r="AE1" t="str">
         <x:v>Retest Needed</x:v>
       </x:c>
-      <x:c r="AF1" s="14" t="str">
+      <x:c r="AF1" t="str">
         <x:v>Notes</x:v>
       </x:c>
     </x:row>
     <x:row r="2">
-      <x:c r="A2" s="15" t="str">
-        <x:v>2026-09-11</x:v>
-      </x:c>
-      <x:c r="B2" s="15" t="str">
+      <x:c r="A2" t="str">
+        <x:v>2026-09-11</x:v>
+      </x:c>
+      <x:c r="B2" t="str">
         <x:v>S0-A — C++ Basic Execution</x:v>
       </x:c>
-      <x:c r="C2" s="15" t="str">
+      <x:c r="C2" t="str">
         <x:v>Intermediate Assessment — Attempt 1</x:v>
       </x:c>
-      <x:c r="D2" s="15" t="str">
-        <x:v>Count and sum positive multiples of 3</x:v>
-      </x:c>
-      <x:c r="E2" s="15" t="str">
+      <x:c r="D2" t="str">
+        <x:v>Positive multiples of 3: count+sum</x:v>
+      </x:c>
+      <x:c r="E2" t="str">
         <x:v>C</x:v>
       </x:c>
-      <x:c r="F2" s="15" t="str">
-        <x:v>Reasoning-only; Tier B pre-validation not completed before exposure</x:v>
-      </x:c>
-      <x:c r="G2" s="15" t="str">
+      <x:c r="F2" t="str">
+        <x:v>Pre-validation incomplete; exposure defect</x:v>
+      </x:c>
+      <x:c r="G2" t="str">
         <x:v>R1</x:v>
       </x:c>
-      <x:c r="H2" s="15" t="str">
+      <x:c r="H2" t="str">
         <x:v>I1</x:v>
       </x:c>
-      <x:c r="I2" s="15" t="str">
+      <x:c r="I2" t="str">
         <x:v>Comparative / Provisional</x:v>
       </x:c>
-      <x:c r="J2" s="15" t="str">
-        <x:v>CP_Calibration_Anchor_Registry_v1.1</x:v>
-      </x:c>
-      <x:c r="K2" s="15" t="str">
-        <x:v>Basic execution: input + condition + loop + function</x:v>
-      </x:c>
-      <x:c r="L2" s="15" t="str">
+      <x:c r="J2" t="str">
+        <x:v>v1.1</x:v>
+      </x:c>
+      <x:c r="K2" t="str">
+        <x:v>I/O + branch + loop + function</x:v>
+      </x:c>
+      <x:c r="L2" t="str">
         <x:v>Incomplete</x:v>
       </x:c>
-      <x:c r="M2" s="15" t="str">
+      <x:c r="M2" t="str">
         <x:v>Immediate</x:v>
       </x:c>
-      <x:c r="O2" s="15" t="n">
-        <x:v>9.166666666666666</x:v>
-      </x:c>
-      <x:c r="U2" s="15" t="str">
+      <x:c r="N2"/>
+      <x:c r="O2" t="n">
+        <x:v>9.1667</x:v>
+      </x:c>
+      <x:c r="P2"/>
+      <x:c r="Q2"/>
+      <x:c r="R2"/>
+      <x:c r="S2"/>
+      <x:c r="T2"/>
+      <x:c r="U2" t="str">
         <x:v>No</x:v>
       </x:c>
-      <x:c r="V2" s="15" t="str">
+      <x:c r="V2" t="str">
         <x:v>GPT-provided</x:v>
       </x:c>
-      <x:c r="W2" s="15" t="str">
+      <x:c r="W2" t="str">
         <x:v>VOID</x:v>
       </x:c>
-      <x:c r="X2" s="15" t="str">
-        <x:v>N/A</x:v>
-      </x:c>
-      <x:c r="Y2" s="15" t="str">
-        <x:v>missing input read for N; required helper function absent; no edge-case validation</x:v>
-      </x:c>
-      <x:c r="Z2" s="15" t="str">
+      <x:c r="X2" t="str">
+        <x:v>N/A</x:v>
+      </x:c>
+      <x:c r="Y2" t="str">
+        <x:v>Evaluator-side defect</x:v>
+      </x:c>
+      <x:c r="Z2" t="str">
         <x:v>L2</x:v>
       </x:c>
-      <x:c r="AA2" s="15" t="str">
+      <x:c r="AA2" t="str">
         <x:v>Provisional</x:v>
       </x:c>
-      <x:c r="AB2" s="15" t="str">
-        <x:v>Baseline; Immediate diagnostic (VOID, not mastery evidence)</x:v>
-      </x:c>
-      <x:c r="AC2" s="15" t="str">
+      <x:c r="AB2" t="str">
+        <x:v>Immediate diagnostic</x:v>
+      </x:c>
+      <x:c r="AC2" t="str">
         <x:v>None</x:v>
       </x:c>
-      <x:c r="AD2" s="15" t="str">
-        <x:v>N/A</x:v>
-      </x:c>
-      <x:c r="AE2" s="15" t="str">
+      <x:c r="AD2" t="str">
+        <x:v>N/A</x:v>
+      </x:c>
+      <x:c r="AE2" t="str">
         <x:v>Yes</x:v>
       </x:c>
-      <x:c r="AF2" s="15" t="str">
-        <x:v>Evaluator-side defect: generated problem was not cross-validated to Tier B before formal use, and the prompt exposed a solution-relevant direction ('process while reading; vector not needed'). Attempt is not formal mastery evidence. Diagnostic only: N remains 0 because cin &gt;&gt; N is missing, so the loop never executes and output is always 0 0; the required non-main function was not implemented. The stated O(N)/O(1) complexity describes the intended design after fixing input, not the submitted program.</x:v>
+      <x:c r="AF2" t="str">
+        <x:v>Not mastery evidence.</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
@@ -620,13 +505,13 @@
         <x:v>Intermediate Assessment — Retest 1</x:v>
       </x:c>
       <x:c r="D3" t="str">
-        <x:v>Transform and sum by sign/parity</x:v>
+        <x:v>Transform+sum by sign/parity</x:v>
       </x:c>
       <x:c r="E3" t="str">
         <x:v>B</x:v>
       </x:c>
       <x:c r="F3" t="str">
-        <x:v>Reference execution + boundary tests + randomized differential verification</x:v>
+        <x:v>Compile + boundary + differential</x:v>
       </x:c>
       <x:c r="G3" t="str">
         <x:v>R1</x:v>
@@ -638,10 +523,10 @@
         <x:v>Comparative / Provisional</x:v>
       </x:c>
       <x:c r="J3" t="str">
-        <x:v>CP_Calibration_Anchor_Registry_v1.1</x:v>
+        <x:v>v1.1</x:v>
       </x:c>
       <x:c r="K3" t="str">
-        <x:v>Basic execution: input + conditional branching + loop + helper function + scalar accumulation</x:v>
+        <x:v>I/O + branch + loop + function</x:v>
       </x:c>
       <x:c r="L3" t="str">
         <x:v>Sufficient for Provisional</x:v>
@@ -651,7 +536,7 @@
       </x:c>
       <x:c r="N3"/>
       <x:c r="O3" t="n">
-        <x:v>4.666666666666667</x:v>
+        <x:v>4.6667</x:v>
       </x:c>
       <x:c r="P3"/>
       <x:c r="Q3"/>
@@ -671,7 +556,7 @@
         <x:v>N/A</x:v>
       </x:c>
       <x:c r="Y3" t="str">
-        <x:v>No correctness error. Explicit edge-case self-check was not listed.</x:v>
+        <x:v>None</x:v>
       </x:c>
       <x:c r="Z3" t="str">
         <x:v>L3</x:v>
@@ -692,7 +577,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="AF3" t="str">
-        <x:v>Clean independent retest. Submitted program compiles and is correct on the sample, boundary-oriented tests, and randomized differential checks. Required helper function is defined and called. O(N) time and O(1) extra-space explanations are correct. No edge case was explicitly listed, but the implementation handles key categories including x&lt;0, x=0, positive even/odd values, N=1, and input bounds; omission of an explicit self-check is retained as a process note rather than a correctness failure. Proceed to Part F final assessment.</x:v>
+        <x:v>Clean independent retest.</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
@@ -706,13 +591,13 @@
         <x:v>Final Assessment — Attempt 1</x:v>
       </x:c>
       <x:c r="D4" t="str">
-        <x:v>Longest contiguous nonzero sign-alternating segment</x:v>
+        <x:v>Longest nonzero sign-alternating segment</x:v>
       </x:c>
       <x:c r="E4" t="str">
         <x:v>B</x:v>
       </x:c>
       <x:c r="F4" t="str">
-        <x:v>Reference execution + exhaustive small-case verification + randomized differential verification</x:v>
+        <x:v>Reference + exhaustive + differential</x:v>
       </x:c>
       <x:c r="G4" t="str">
         <x:v>R1</x:v>
@@ -724,10 +609,10 @@
         <x:v>Comparative / Provisional</x:v>
       </x:c>
       <x:c r="J4" t="str">
-        <x:v>CP_Calibration_Anchor_Registry_v1.1</x:v>
+        <x:v>v1.1</x:v>
       </x:c>
       <x:c r="K4" t="str">
-        <x:v>Basic execution: input + conditional branching + loop + helper function + scalar state tracking</x:v>
+        <x:v>Scalar state + boundary handling</x:v>
       </x:c>
       <x:c r="L4" t="str">
         <x:v>Incomplete</x:v>
@@ -737,7 +622,7 @@
       </x:c>
       <x:c r="N4"/>
       <x:c r="O4" t="n">
-        <x:v>28.716666666666665</x:v>
+        <x:v>28.7167</x:v>
       </x:c>
       <x:c r="P4"/>
       <x:c r="Q4"/>
@@ -757,7 +642,7 @@
         <x:v>Correctness</x:v>
       </x:c>
       <x:c r="Y4" t="str">
-        <x:v>Important zero-boundary handling failure; first zero counted as length 1; zero/nonzero transition unconditionally resets current length to 0; no edge-case self-check</x:v>
+        <x:v>Zero-boundary state transitions</x:v>
       </x:c>
       <x:c r="Z4" t="str">
         <x:v>L3</x:v>
@@ -778,7 +663,7 @@
         <x:v>Yes</x:v>
       </x:c>
       <x:c r="AF4" t="str">
-        <x:v>Core O(N)/O(1) state-tracking idea is viable and sample/nonzero alternating cases work, but important zero cases fail. Counterexamples: N=1,[0] returns 1 instead of 0; [0,5,-3] returns 1 instead of 2. The duplicated unconditional `sum1 = 0;` inside the zero-product branch erases a valid new length-1 segment when previous value is zero and current value is nonzero. First-element logic also counts zero as a valid segment. First formal final-assessment FAIL; per v5.4 §39.1, convert this problem to learning mode, remediate, then reassess with a new equivalent problem.</x:v>
+        <x:v>Remediation required.</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -792,13 +677,13 @@
         <x:v>Final Assessment — Retest 1</x:v>
       </x:c>
       <x:c r="D5" t="str">
-        <x:v>Balance recovery count and maximum post-transaction balance</x:v>
+        <x:v>Recovery count + max balance</x:v>
       </x:c>
       <x:c r="E5" t="str">
         <x:v>B</x:v>
       </x:c>
       <x:c r="F5" t="str">
-        <x:v>Reference execution + exhaustive small-case verification + randomized differential verification</x:v>
+        <x:v>Reference + exhaustive + differential</x:v>
       </x:c>
       <x:c r="G5" t="str">
         <x:v>R1</x:v>
@@ -810,10 +695,10 @@
         <x:v>Comparative / Provisional</x:v>
       </x:c>
       <x:c r="J5" t="str">
-        <x:v>CP_Calibration_Anchor_Registry_v1.1</x:v>
+        <x:v>v1.1</x:v>
       </x:c>
       <x:c r="K5" t="str">
-        <x:v>Basic execution: input + conditional branching + loop + helper function + scalar state tracking + initial-state handling</x:v>
+        <x:v>Scalar state + initial transition</x:v>
       </x:c>
       <x:c r="L5" t="str">
         <x:v>Incomplete</x:v>
@@ -843,7 +728,7 @@
         <x:v>Correctness</x:v>
       </x:c>
       <x:c r="Y5" t="str">
-        <x:v>Initial-state transition omitted: first transaction from balance 0 to positive is a recovery; no edge-case self-check; repeated boundary/initialization validation failure</x:v>
+        <x:v>First transition omitted; no edge self-check</x:v>
       </x:c>
       <x:c r="Z5" t="str">
         <x:v>L3</x:v>
@@ -864,7 +749,7 @@
         <x:v>Yes</x:v>
       </x:c>
       <x:c r="AF5" t="str">
-        <x:v>Core O(N)/O(1) design and maximum-balance tracking are sound, but the special-case first iteration skips recovery detection. Counterexample: N=1, x=5 should output `1 5`, but submitted code outputs `0 5`. This is the second consecutive skill-related final-assessment FAIL on the same Learning Objective, with repeated boundary/edge-case validation weakness. Per v5.4 §39.2, pause formal retesting and perform diagnostic remediation before another new formal final-assessment problem.</x:v>
+        <x:v>Second consecutive same-objective FAIL.</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
@@ -878,13 +763,13 @@
         <x:v>Final Assessment — Retest 2</x:v>
       </x:c>
       <x:c r="D6" t="str">
-        <x:v>Record-break count and longest contiguous increasing segment</x:v>
+        <x:v>Record breaks + longest increasing segment</x:v>
       </x:c>
       <x:c r="E6" t="str">
         <x:v>B</x:v>
       </x:c>
       <x:c r="F6" t="str">
-        <x:v>Exact-code compilation + sample/boundary execution + exhaustive small-case differential verification</x:v>
+        <x:v>Compile + boundary + exhaustive differential</x:v>
       </x:c>
       <x:c r="G6" t="str">
         <x:v>R1</x:v>
@@ -896,20 +781,20 @@
         <x:v>Comparative / Provisional</x:v>
       </x:c>
       <x:c r="J6" t="str">
-        <x:v>CP_Calibration_Anchor_Registry_v1.1</x:v>
+        <x:v>v1.1</x:v>
       </x:c>
       <x:c r="K6" t="str">
-        <x:v>Basic execution: input + conditional branching + loop + helper function + scalar state tracking + initialization/boundary handling</x:v>
+        <x:v>State + initialization/boundary</x:v>
       </x:c>
       <x:c r="L6" t="str">
         <x:v>Sufficient for Provisional</x:v>
       </x:c>
       <x:c r="M6" t="str">
-        <x:v>Immediate; Compiler/Debugger allowed</x:v>
+        <x:v>Immediate; compiler/debugger allowed</x:v>
       </x:c>
       <x:c r="N6"/>
       <x:c r="O6" t="n">
-        <x:v>33.06666666666667</x:v>
+        <x:v>33.0667</x:v>
       </x:c>
       <x:c r="P6"/>
       <x:c r="Q6"/>
@@ -929,7 +814,7 @@
         <x:v>N/A</x:v>
       </x:c>
       <x:c r="Y6" t="str">
-        <x:v>No correctness error. Learner explicitly self-checked N=1 =&gt; 1 1. VS debugger use was permitted but actual use was not reported.</x:v>
+        <x:v>None</x:v>
       </x:c>
       <x:c r="Z6" t="str">
         <x:v>L3</x:v>
@@ -938,7 +823,7 @@
         <x:v>Provisional</x:v>
       </x:c>
       <x:c r="AB6" t="str">
-        <x:v>Immediate; Compiler/Debugger allowed</x:v>
+        <x:v>Immediate</x:v>
       </x:c>
       <x:c r="AC6" t="str">
         <x:v>Resolved</x:v>
@@ -950,7 +835,93 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="AF6" t="str">
-        <x:v>Clean independent final retest after diagnostic remediation. Exact code compiled under C++17 and matched the sample, boundary executions, and exhaustive small-case differential checks. Record-break logic is correct because a new record is necessarily greater than the immediately previous value, so incrementing the current increasing-run length in that branch is valid. O(N) time and O(1) extra-space analyses are correct. Repeated initial/boundary-state weakness is considered remediated at immediate-evidence level; proceed to mandatory Part G Adaptive Extra Problem.</x:v>
+        <x:v>Explicit N=1 check; clean PASS.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" t="str">
+        <x:v>2026-09-11</x:v>
+      </x:c>
+      <x:c r="B7" t="str">
+        <x:v>S0-A — C++ Basic Execution</x:v>
+      </x:c>
+      <x:c r="C7" t="str">
+        <x:v>Adaptive Extra Problem</x:v>
+      </x:c>
+      <x:c r="D7" t="str">
+        <x:v>Min cumulative balance + longest negative streak</x:v>
+      </x:c>
+      <x:c r="E7" t="str">
+        <x:v>B</x:v>
+      </x:c>
+      <x:c r="F7" t="str">
+        <x:v>Compile + boundary + exhaustive differential</x:v>
+      </x:c>
+      <x:c r="G7" t="str">
+        <x:v>R1</x:v>
+      </x:c>
+      <x:c r="H7" t="str">
+        <x:v>I2</x:v>
+      </x:c>
+      <x:c r="I7" t="str">
+        <x:v>Comparative / Provisional</x:v>
+      </x:c>
+      <x:c r="J7" t="str">
+        <x:v>v1.1</x:v>
+      </x:c>
+      <x:c r="K7" t="str">
+        <x:v>Cumulative state + reset + numeric safety</x:v>
+      </x:c>
+      <x:c r="L7" t="str">
+        <x:v>Complete — Progression Gate Satisfied</x:v>
+      </x:c>
+      <x:c r="M7" t="str">
+        <x:v>Immediate; compiler/debugger allowed</x:v>
+      </x:c>
+      <x:c r="N7"/>
+      <x:c r="O7" t="n">
+        <x:v>14.6833</x:v>
+      </x:c>
+      <x:c r="P7"/>
+      <x:c r="Q7"/>
+      <x:c r="R7"/>
+      <x:c r="S7"/>
+      <x:c r="T7"/>
+      <x:c r="U7" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="V7" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="W7" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="X7" t="str">
+        <x:v>N/A</x:v>
+      </x:c>
+      <x:c r="Y7" t="str">
+        <x:v>Unused r only</x:v>
+      </x:c>
+      <x:c r="Z7" t="str">
+        <x:v>L3</x:v>
+      </x:c>
+      <x:c r="AA7" t="str">
+        <x:v>Provisional</x:v>
+      </x:c>
+      <x:c r="AB7" t="str">
+        <x:v>Immediate</x:v>
+      </x:c>
+      <x:c r="AC7" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="AD7" t="str">
+        <x:v>N/A</x:v>
+      </x:c>
+      <x:c r="AE7" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="AF7" t="str">
+        <x:v>Part G PASS; explicit N=1 checks; S0-A A-H complete.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -961,191 +932,181 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
-  <x:cols>
-    <x:col min="1" max="1" width="10" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="26" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="16" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="12" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="16" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="22" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="14" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="14" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="14" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="14" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="32" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="45" hidden="0" customWidth="1"/>
-  </x:cols>
   <x:sheetData>
-    <x:row r="1" ht="42" hidden="0" customHeight="1">
-      <x:c r="A1" s="14" t="str">
+    <x:row r="1">
+      <x:c r="A1" t="str">
         <x:v>Stage</x:v>
       </x:c>
-      <x:c r="B1" s="14" t="str">
+      <x:c r="B1" t="str">
         <x:v>Learning Unit</x:v>
       </x:c>
-      <x:c r="C1" s="14" t="str">
+      <x:c r="C1" t="str">
         <x:v>Priority Class</x:v>
       </x:c>
-      <x:c r="D1" s="14" t="str">
+      <x:c r="D1" t="str">
         <x:v>Capability</x:v>
       </x:c>
-      <x:c r="E1" s="14" t="str">
+      <x:c r="E1" t="str">
         <x:v>Confidence</x:v>
       </x:c>
-      <x:c r="F1" s="14" t="str">
+      <x:c r="F1" t="str">
         <x:v>Evidence Context</x:v>
       </x:c>
-      <x:c r="G1" s="14" t="str">
+      <x:c r="G1" t="str">
         <x:v>Unit Coverage Status</x:v>
       </x:c>
-      <x:c r="H1" s="14" t="str">
+      <x:c r="H1" t="str">
         <x:v>Review Debt</x:v>
       </x:c>
-      <x:c r="I1" s="14" t="str">
+      <x:c r="I1" t="str">
         <x:v>Review Debt Severity</x:v>
       </x:c>
-      <x:c r="J1" s="14" t="str">
+      <x:c r="J1" t="str">
         <x:v>Retest Needed</x:v>
       </x:c>
-      <x:c r="K1" s="14" t="str">
+      <x:c r="K1" t="str">
         <x:v>Last Assessed</x:v>
       </x:c>
-      <x:c r="L1" s="14" t="str">
+      <x:c r="L1" t="str">
         <x:v>Next Review</x:v>
       </x:c>
-      <x:c r="M1" s="14" t="str">
+      <x:c r="M1" t="str">
         <x:v>Current Bottleneck</x:v>
       </x:c>
-      <x:c r="N1" s="14" t="str">
+      <x:c r="N1" t="str">
         <x:v>Notes</x:v>
       </x:c>
     </x:row>
-    <x:row r="2" ht="42" hidden="0" customHeight="1">
-      <x:c r="A2" s="18" t="str">
+    <x:row r="2">
+      <x:c r="A2" t="str">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="B2" s="18" t="str">
+      <x:c r="B2" t="str">
         <x:v>S0-A — C++ Basic Execution</x:v>
       </x:c>
-      <x:c r="C2" s="18" t="str">
+      <x:c r="C2" t="str">
         <x:v>Core</x:v>
       </x:c>
-      <x:c r="D2" s="18" t="str">
+      <x:c r="D2" t="str">
         <x:v>L3</x:v>
       </x:c>
-      <x:c r="E2" s="18" t="str">
+      <x:c r="E2" t="str">
         <x:v>Provisional</x:v>
       </x:c>
-      <x:c r="F2" s="18" t="str">
+      <x:c r="F2" t="str">
         <x:v>Immediate</x:v>
       </x:c>
-      <x:c r="G2" s="18" t="str">
-        <x:v>Sufficient for Provisional</x:v>
-      </x:c>
-      <x:c r="H2" s="18" t="str">
-        <x:v>Resolved</x:v>
-      </x:c>
-      <x:c r="I2" s="18" t="str">
-        <x:v>N/A</x:v>
-      </x:c>
-      <x:c r="J2" s="18" t="str">
+      <x:c r="G2" t="str">
+        <x:v>Complete — Progression Gate Satisfied</x:v>
+      </x:c>
+      <x:c r="H2" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="I2" t="str">
+        <x:v>N/A</x:v>
+      </x:c>
+      <x:c r="J2" t="str">
         <x:v>No</x:v>
       </x:c>
-      <x:c r="K2" s="18" t="str">
+      <x:c r="K2" t="str">
         <x:v>2026-09-11</x:v>
       </x:c>
       <x:c r="L2" t="str">
-        <x:v>Part G Adaptive Extra Problem</x:v>
-      </x:c>
-      <x:c r="M2" s="18" t="str">
-        <x:v>No blocking correctness issue remains in immediate evidence; continue explicit edge-case validation habit.</x:v>
-      </x:c>
-      <x:c r="N2" s="18" t="str">
-        <x:v>Intermediate retest PASS and Final Retest 2 PASS. Diagnostic remediation checkpoint correctly articulated state meanings and first-transition handling. Medium Review Debt from repeated boundary/initial-state errors resolved after clean final retest. Long-term confidence remains Provisional pending delayed/mixed evidence.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="3" ht="42" hidden="0" customHeight="1">
-      <x:c r="A3" s="18" t="str">
+        <x:v>Delayed/Mixed Assessment</x:v>
+      </x:c>
+      <x:c r="M2" t="str">
+        <x:v>Monitor boundary/edge-case validation transfer</x:v>
+      </x:c>
+      <x:c r="N2" t="str">
+        <x:v>A-H complete; later Confirmed evidence needed.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" t="str">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="B3" s="18" t="str">
+      <x:c r="B3" t="str">
         <x:v>S0-B — Basic Containers &amp; STL</x:v>
       </x:c>
-      <x:c r="C3" s="18" t="str">
+      <x:c r="C3" t="str">
         <x:v>Core</x:v>
       </x:c>
-      <x:c r="D3" s="18" t="str">
+      <x:c r="D3" t="str">
         <x:v>L1</x:v>
       </x:c>
-      <x:c r="E3" s="18" t="str">
+      <x:c r="E3" t="str">
         <x:v>Provisional</x:v>
       </x:c>
-      <x:c r="F3" s="18" t="str">
+      <x:c r="F3" t="str">
         <x:v>Baseline</x:v>
       </x:c>
-      <x:c r="G3" s="18" t="str">
-        <x:v>N/A</x:v>
-      </x:c>
-      <x:c r="H3" s="18" t="str">
+      <x:c r="G3" t="str">
+        <x:v>N/A</x:v>
+      </x:c>
+      <x:c r="H3" t="str">
         <x:v>None</x:v>
       </x:c>
-      <x:c r="I3" s="18" t="str">
-        <x:v>N/A</x:v>
-      </x:c>
-      <x:c r="J3" s="18" t="str">
+      <x:c r="I3" t="str">
+        <x:v>N/A</x:v>
+      </x:c>
+      <x:c r="J3" t="str">
         <x:v>Yes</x:v>
       </x:c>
-      <x:c r="K3" s="18" t="str">
-        <x:v>2026-09-11</x:v>
-      </x:c>
-      <x:c r="M3" s="18" t="str">
-        <x:v>vector construction/manipulation and basic STL syntax are a clear knowledge gap.</x:v>
-      </x:c>
-      <x:c r="N3" s="18" t="str">
-        <x:v>Baseline Problem A/B both exposed vector/STL implementation gaps.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4" ht="42" hidden="0" customHeight="1">
-      <x:c r="A4" s="18" t="str">
+      <x:c r="K3" t="str">
+        <x:v>2026-09-11</x:v>
+      </x:c>
+      <x:c r="L3" t="str">
+        <x:v>During S0-B</x:v>
+      </x:c>
+      <x:c r="M3" t="str">
+        <x:v>vector/STL syntax and manipulation</x:v>
+      </x:c>
+      <x:c r="N3" t="str">
+        <x:v>Baseline A/B exposed gap.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" t="str">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="B4" s="18" t="str">
+      <x:c r="B4" t="str">
         <x:v>S0-C — Complexity &amp; Numeric Safety</x:v>
       </x:c>
-      <x:c r="C4" s="18" t="str">
+      <x:c r="C4" t="str">
         <x:v>Core</x:v>
       </x:c>
-      <x:c r="D4" s="18" t="str">
+      <x:c r="D4" t="str">
         <x:v>L2</x:v>
       </x:c>
-      <x:c r="E4" s="18" t="str">
+      <x:c r="E4" t="str">
         <x:v>Provisional</x:v>
       </x:c>
-      <x:c r="F4" s="18" t="str">
+      <x:c r="F4" t="str">
         <x:v>Baseline</x:v>
       </x:c>
-      <x:c r="G4" s="18" t="str">
-        <x:v>N/A</x:v>
-      </x:c>
-      <x:c r="H4" s="18" t="str">
+      <x:c r="G4" t="str">
+        <x:v>N/A</x:v>
+      </x:c>
+      <x:c r="H4" t="str">
         <x:v>None</x:v>
       </x:c>
-      <x:c r="I4" s="18" t="str">
-        <x:v>N/A</x:v>
-      </x:c>
-      <x:c r="J4" s="18" t="str">
+      <x:c r="I4" t="str">
+        <x:v>N/A</x:v>
+      </x:c>
+      <x:c r="J4" t="str">
         <x:v>Yes</x:v>
       </x:c>
-      <x:c r="K4" s="18" t="str">
-        <x:v>2026-09-11</x:v>
-      </x:c>
-      <x:c r="M4" s="18" t="str">
-        <x:v>Understands O(N log N) loop composition and multiplication overflow, but misclassified sort and failed to apply numeric bounds consistently.</x:v>
-      </x:c>
-      <x:c r="N4" s="18" t="str">
-        <x:v>Needs explicit constraint-to-type and operation-complexity verification habits.</x:v>
+      <x:c r="K4" t="str">
+        <x:v>2026-09-11</x:v>
+      </x:c>
+      <x:c r="L4" t="str">
+        <x:v>During S0-C</x:v>
+      </x:c>
+      <x:c r="M4" t="str">
+        <x:v>operation complexity + constraint-to-type consistency</x:v>
+      </x:c>
+      <x:c r="N4" t="str">
+        <x:v>Baseline evidence.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -1156,44 +1117,33 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
-  <x:cols>
-    <x:col min="1" max="1" width="10" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="24" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="38" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="22" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="28" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="14" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="45" hidden="0" customWidth="1"/>
-  </x:cols>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" s="14" t="str">
+      <x:c r="A1" t="str">
         <x:v>Stage</x:v>
       </x:c>
-      <x:c r="B1" s="14" t="str">
+      <x:c r="B1" t="str">
         <x:v>Learning Unit</x:v>
       </x:c>
-      <x:c r="C1" s="14" t="str">
-        <x:v>Core Decision Boundary</x:v>
-      </x:c>
-      <x:c r="D1" s="14" t="str">
+      <x:c r="C1" t="str">
+        <x:v>Decision Boundary</x:v>
+      </x:c>
+      <x:c r="D1" t="str">
         <x:v>Status</x:v>
       </x:c>
-      <x:c r="E1" s="14" t="str">
-        <x:v>Evidence Context</x:v>
-      </x:c>
-      <x:c r="F1" s="14" t="str">
-        <x:v>Assessment Type</x:v>
-      </x:c>
-      <x:c r="G1" s="14" t="str">
-        <x:v>Problem</x:v>
-      </x:c>
-      <x:c r="H1" s="14" t="str">
-        <x:v>Date</x:v>
-      </x:c>
-      <x:c r="I1" s="14" t="str">
+      <x:c r="E1" t="str">
+        <x:v>Evidence</x:v>
+      </x:c>
+      <x:c r="F1" t="str">
+        <x:v>Assessment</x:v>
+      </x:c>
+      <x:c r="G1" t="str">
+        <x:v>R</x:v>
+      </x:c>
+      <x:c r="H1" t="str">
+        <x:v>I</x:v>
+      </x:c>
+      <x:c r="I1" t="str">
         <x:v>Notes</x:v>
       </x:c>
     </x:row>
@@ -1205,52 +1155,39 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
-  <x:cols>
-    <x:col min="1" max="1" width="14" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="10" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="24" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="12" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="36" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="14" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="36" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="14" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="14" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="45" hidden="0" customWidth="1"/>
-  </x:cols>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" s="14" t="str">
+      <x:c r="A1" t="str">
         <x:v>Opened</x:v>
       </x:c>
-      <x:c r="B1" s="14" t="str">
+      <x:c r="B1" t="str">
         <x:v>Stage</x:v>
       </x:c>
-      <x:c r="C1" s="14" t="str">
+      <x:c r="C1" t="str">
         <x:v>Learning Unit</x:v>
       </x:c>
-      <x:c r="D1" s="14" t="str">
+      <x:c r="D1" t="str">
         <x:v>Severity</x:v>
       </x:c>
-      <x:c r="E1" s="14" t="str">
+      <x:c r="E1" t="str">
         <x:v>Reason</x:v>
       </x:c>
-      <x:c r="F1" s="14" t="str">
+      <x:c r="F1" t="str">
         <x:v>Prerequisite Blocking?</x:v>
       </x:c>
-      <x:c r="G1" s="14" t="str">
+      <x:c r="G1" t="str">
         <x:v>Status</x:v>
       </x:c>
-      <x:c r="H1" s="14" t="str">
+      <x:c r="H1" t="str">
         <x:v>Next Remediation</x:v>
       </x:c>
-      <x:c r="I1" s="14" t="str">
+      <x:c r="I1" t="str">
         <x:v>Next Review</x:v>
       </x:c>
-      <x:c r="J1" s="14" t="str">
+      <x:c r="J1" t="str">
         <x:v>Resolved</x:v>
       </x:c>
-      <x:c r="K1" s="14" t="str">
+      <x:c r="K1" t="str">
         <x:v>Notes</x:v>
       </x:c>
     </x:row>
@@ -1268,7 +1205,7 @@
         <x:v>Medium</x:v>
       </x:c>
       <x:c r="E2" t="str">
-        <x:v>Repeated boundary/initial-state correctness errors and no explicit edge-case self-validation across two consecutive final assessments.</x:v>
+        <x:v>Repeated boundary/initial-state errors and missing edge checks</x:v>
       </x:c>
       <x:c r="F2" t="str">
         <x:v>Yes</x:v>
@@ -1277,7 +1214,7 @@
         <x:v>Resolved</x:v>
       </x:c>
       <x:c r="H2" t="str">
-        <x:v>Maintain mandatory explicit minimum/boundary-case self-check in future assessments; watch for recurrence in delayed/mixed evidence.</x:v>
+        <x:v>Monitor recurrence</x:v>
       </x:c>
       <x:c r="I2" t="str">
         <x:v>Delayed/Mixed Assessment</x:v>
@@ -1286,7 +1223,7 @@
         <x:v>2026-09-11</x:v>
       </x:c>
       <x:c r="K2" t="str">
-        <x:v>Diagnostic remediation checkpoint passed; subsequent Final Assessment Retest 2 passed independently with explicit N=1 edge-case check. Debt resolved, but recurrence should reopen debt.</x:v>
+        <x:v>Resolved after remediation + Final Retest 2 PASS + Extra PASS.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -1297,277 +1234,313 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
-  <x:cols>
-    <x:col min="1" max="1" width="12" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="34" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="14" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="8" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="8" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="18" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="14" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="16" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="16" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="16" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="24" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="38" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="38" hidden="0" customWidth="1"/>
-    <x:col min="16" max="16" width="60" hidden="0" customWidth="1"/>
-  </x:cols>
   <x:sheetData>
-    <x:row r="1" ht="36" hidden="0" customHeight="1">
-      <x:c r="A1" s="14" t="str">
+    <x:row r="1">
+      <x:c r="A1" t="str">
         <x:v>Date</x:v>
       </x:c>
-      <x:c r="B1" s="14" t="str">
+      <x:c r="B1" t="str">
         <x:v>Block</x:v>
       </x:c>
-      <x:c r="C1" s="14" t="str">
+      <x:c r="C1" t="str">
         <x:v>Problem</x:v>
       </x:c>
-      <x:c r="D1" s="14" t="str">
+      <x:c r="D1" t="str">
         <x:v>Validation Tier</x:v>
       </x:c>
-      <x:c r="E1" s="14" t="str">
+      <x:c r="E1" t="str">
         <x:v>R</x:v>
       </x:c>
-      <x:c r="F1" s="14" t="str">
+      <x:c r="F1" t="str">
         <x:v>I</x:v>
       </x:c>
-      <x:c r="G1" s="14" t="str">
+      <x:c r="G1" t="str">
         <x:v>Result</x:v>
       </x:c>
-      <x:c r="H1" s="14" t="str">
+      <x:c r="H1" t="str">
         <x:v>T_solve (min)</x:v>
       </x:c>
-      <x:c r="I1" s="14" t="str">
+      <x:c r="I1" t="str">
         <x:v>T_recognition (min)</x:v>
       </x:c>
-      <x:c r="J1" s="14" t="str">
+      <x:c r="J1" t="str">
         <x:v>T_implementation (min)</x:v>
       </x:c>
-      <x:c r="K1" s="14" t="str">
+      <x:c r="K1" t="str">
         <x:v>T_validation_debug (min)</x:v>
       </x:c>
-      <x:c r="L1" s="14" t="str">
+      <x:c r="L1" t="str">
         <x:v>First-pass Correct</x:v>
       </x:c>
-      <x:c r="M1" s="14" t="str">
+      <x:c r="M1" t="str">
         <x:v>Failure Attribution</x:v>
       </x:c>
-      <x:c r="N1" s="14" t="str">
+      <x:c r="N1" t="str">
         <x:v>Error Types</x:v>
       </x:c>
-      <x:c r="O1" s="14" t="str">
+      <x:c r="O1" t="str">
         <x:v>Knowledge Coverage Gap</x:v>
       </x:c>
-      <x:c r="P1" s="14" t="str">
+      <x:c r="P1" t="str">
         <x:v>Notes</x:v>
       </x:c>
     </x:row>
-    <x:row r="2" ht="36" hidden="0" customHeight="1">
-      <x:c r="A2" s="18" t="str">
-        <x:v>2026-09-11</x:v>
-      </x:c>
-      <x:c r="B2" s="18" t="str">
-        <x:v>Foundation Check</x:v>
-      </x:c>
-      <x:c r="C2" s="18" t="str">
-        <x:v>FC-1 — even count + sum</x:v>
-      </x:c>
-      <x:c r="D2" s="18" t="str">
+    <x:row r="2">
+      <x:c r="A2" t="str">
+        <x:v>2026-09-11</x:v>
+      </x:c>
+      <x:c r="B2" t="str">
+        <x:v>FC-1</x:v>
+      </x:c>
+      <x:c r="C2" t="str">
+        <x:v>Even count + sum</x:v>
+      </x:c>
+      <x:c r="D2" t="str">
+        <x:v>N/A</x:v>
+      </x:c>
+      <x:c r="E2" t="str">
+        <x:v>R1</x:v>
+      </x:c>
+      <x:c r="F2" t="str">
+        <x:v>I1</x:v>
+      </x:c>
+      <x:c r="G2" t="str">
+        <x:v>CONDITIONAL PASS</x:v>
+      </x:c>
+      <x:c r="H2"/>
+      <x:c r="I2"/>
+      <x:c r="J2"/>
+      <x:c r="K2"/>
+      <x:c r="L2" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="M2" t="str">
+        <x:v>Numeric Safety</x:v>
+      </x:c>
+      <x:c r="N2" t="str">
+        <x:v>int sum overflow risk</x:v>
+      </x:c>
+      <x:c r="O2" t="str">
+        <x:v>constraint-to-type</x:v>
+      </x:c>
+      <x:c r="P2" t="str">
+        <x:v>Reported 6:58 excluded reading.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" t="str">
+        <x:v>2026-09-11</x:v>
+      </x:c>
+      <x:c r="B3" t="str">
+        <x:v>FC-2</x:v>
+      </x:c>
+      <x:c r="C3" t="str">
+        <x:v>Nested loop complexity</x:v>
+      </x:c>
+      <x:c r="D3" t="str">
+        <x:v>N/A</x:v>
+      </x:c>
+      <x:c r="E3" t="str">
+        <x:v>R1</x:v>
+      </x:c>
+      <x:c r="F3" t="str">
+        <x:v>I1</x:v>
+      </x:c>
+      <x:c r="G3" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="H3"/>
+      <x:c r="I3"/>
+      <x:c r="J3"/>
+      <x:c r="K3"/>
+      <x:c r="L3" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="M3" t="str">
+        <x:v>N/A</x:v>
+      </x:c>
+      <x:c r="N3" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="O3" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="P3" t="str">
+        <x:v>O(N log N); reported 3:48 excluded reading.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" t="str">
+        <x:v>2026-09-11</x:v>
+      </x:c>
+      <x:c r="B4" t="str">
+        <x:v>FC-3</x:v>
+      </x:c>
+      <x:c r="C4" t="str">
+        <x:v>int multiplication overflow</x:v>
+      </x:c>
+      <x:c r="D4" t="str">
+        <x:v>N/A</x:v>
+      </x:c>
+      <x:c r="E4" t="str">
+        <x:v>R1</x:v>
+      </x:c>
+      <x:c r="F4" t="str">
+        <x:v>I1</x:v>
+      </x:c>
+      <x:c r="G4" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="H4"/>
+      <x:c r="I4"/>
+      <x:c r="J4"/>
+      <x:c r="K4"/>
+      <x:c r="L4" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="M4" t="str">
+        <x:v>N/A</x:v>
+      </x:c>
+      <x:c r="N4" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="O4" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="P4" t="str">
+        <x:v>Correct promotion; reported 2:18 excluded reading.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" t="str">
+        <x:v>2026-09-11</x:v>
+      </x:c>
+      <x:c r="B5" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="C5" t="str">
+        <x:v>LC977 Squares of Sorted Array</x:v>
+      </x:c>
+      <x:c r="D5" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="E5" t="str">
+        <x:v>R1</x:v>
+      </x:c>
+      <x:c r="F5" t="str">
+        <x:v>I1</x:v>
+      </x:c>
+      <x:c r="G5" t="str">
+        <x:v>FAIL</x:v>
+      </x:c>
+      <x:c r="H5" t="n">
+        <x:v>12.033</x:v>
+      </x:c>
+      <x:c r="I5"/>
+      <x:c r="J5"/>
+      <x:c r="K5"/>
+      <x:c r="L5" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="M5" t="str">
+        <x:v>Implementation / Complexity</x:v>
+      </x:c>
+      <x:c r="N5" t="str">
+        <x:v>vector syntax; sort complexity</x:v>
+      </x:c>
+      <x:c r="O5" t="str">
+        <x:v>vector/STL</x:v>
+      </x:c>
+      <x:c r="P5" t="str">
+        <x:v>Valid square+sort idea.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" t="str">
+        <x:v>2026-09-11</x:v>
+      </x:c>
+      <x:c r="B6" t="str">
+        <x:v>B</x:v>
+      </x:c>
+      <x:c r="C6" t="str">
+        <x:v>LC26 Remove Duplicates</x:v>
+      </x:c>
+      <x:c r="D6" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="E6" t="str">
+        <x:v>R2</x:v>
+      </x:c>
+      <x:c r="F6" t="str">
+        <x:v>I2</x:v>
+      </x:c>
+      <x:c r="G6" t="str">
+        <x:v>FAIL</x:v>
+      </x:c>
+      <x:c r="H6" t="n">
+        <x:v>12.383</x:v>
+      </x:c>
+      <x:c r="I6"/>
+      <x:c r="J6"/>
+      <x:c r="K6"/>
+      <x:c r="L6" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="M6" t="str">
+        <x:v>Contract / Implementation</x:v>
+      </x:c>
+      <x:c r="N6" t="str">
+        <x:v>in-place violation; vector syntax</x:v>
+      </x:c>
+      <x:c r="O6" t="str">
+        <x:v>vector/STL</x:v>
+      </x:c>
+      <x:c r="P6" t="str">
+        <x:v>Sorted-order reasoning partial.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" t="str">
+        <x:v>2026-09-11</x:v>
+      </x:c>
+      <x:c r="B7" t="str">
         <x:v>C</x:v>
       </x:c>
-      <x:c r="G2" s="18" t="str">
-        <x:v>CONDITIONAL PASS</x:v>
-      </x:c>
-      <x:c r="L2" s="18" t="str">
+      <x:c r="C7" t="str">
+        <x:v>LC334 Increasing Triplet</x:v>
+      </x:c>
+      <x:c r="D7" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="E7" t="str">
+        <x:v>R3</x:v>
+      </x:c>
+      <x:c r="F7" t="str">
+        <x:v>I2</x:v>
+      </x:c>
+      <x:c r="G7" t="str">
+        <x:v>FAIL</x:v>
+      </x:c>
+      <x:c r="H7" t="n">
+        <x:v>112.183</x:v>
+      </x:c>
+      <x:c r="I7"/>
+      <x:c r="J7"/>
+      <x:c r="K7"/>
+      <x:c r="L7" t="str">
         <x:v>No</x:v>
       </x:c>
-      <x:c r="M2" s="18" t="str">
+      <x:c r="M7" t="str">
         <x:v>Correctness / Implementation</x:v>
       </x:c>
-      <x:c r="N2" s="18" t="str">
-        <x:v>overflow; numeric type selection</x:v>
-      </x:c>
-      <x:c r="P2" s="18" t="str">
-        <x:v>Reported 6:58 after reading; not treated as valid T_solve. Core loop logic correct, but sum stored in int although worst-case sum is 1e14.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="3" ht="36" hidden="0" customHeight="1">
-      <x:c r="A3" s="18" t="str">
-        <x:v>2026-09-11</x:v>
-      </x:c>
-      <x:c r="B3" s="18" t="str">
-        <x:v>Foundation Check</x:v>
-      </x:c>
-      <x:c r="C3" s="18" t="str">
-        <x:v>FC-2 — nested loop complexity</x:v>
-      </x:c>
-      <x:c r="D3" s="18" t="str">
-        <x:v>C</x:v>
-      </x:c>
-      <x:c r="G3" s="18" t="str">
-        <x:v>PASS</x:v>
-      </x:c>
-      <x:c r="L3" s="18" t="str">
-        <x:v>Yes</x:v>
-      </x:c>
-      <x:c r="M3" s="18" t="str">
-        <x:v>N/A</x:v>
-      </x:c>
-      <x:c r="P3" s="18" t="str">
-        <x:v>Reported 3:48 after reading; not treated as valid T_solve. Correctly derived O(N log N).</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4" ht="36" hidden="0" customHeight="1">
-      <x:c r="A4" s="18" t="str">
-        <x:v>2026-09-11</x:v>
-      </x:c>
-      <x:c r="B4" s="18" t="str">
-        <x:v>Foundation Check</x:v>
-      </x:c>
-      <x:c r="C4" s="18" t="str">
-        <x:v>FC-3 — multiplication overflow</x:v>
-      </x:c>
-      <x:c r="D4" s="18" t="str">
-        <x:v>C</x:v>
-      </x:c>
-      <x:c r="G4" s="18" t="str">
-        <x:v>PASS</x:v>
-      </x:c>
-      <x:c r="L4" s="18" t="str">
-        <x:v>Yes</x:v>
-      </x:c>
-      <x:c r="M4" s="18" t="str">
-        <x:v>N/A</x:v>
-      </x:c>
-      <x:c r="P4" s="18" t="str">
-        <x:v>Reported 2:18 after reading; not treated as valid T_solve. Correctly recognized int multiplication overflow risk and promoted operands to long long.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5" ht="36" hidden="0" customHeight="1">
-      <x:c r="A5" s="18" t="str">
-        <x:v>2026-09-11</x:v>
-      </x:c>
-      <x:c r="B5" s="18" t="str">
-        <x:v>Baseline Problem A</x:v>
-      </x:c>
-      <x:c r="C5" s="18" t="str">
-        <x:v>LeetCode 977 — Squares of a Sorted Array</x:v>
-      </x:c>
-      <x:c r="D5" s="18" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="E5" s="18" t="str">
-        <x:v>R1</x:v>
-      </x:c>
-      <x:c r="F5" s="18" t="str">
-        <x:v>I1</x:v>
-      </x:c>
-      <x:c r="G5" s="18" t="str">
-        <x:v>FAIL</x:v>
-      </x:c>
-      <x:c r="H5" s="18" t="n">
-        <x:v>12.033</x:v>
-      </x:c>
-      <x:c r="L5" s="18" t="str">
-        <x:v>No</x:v>
-      </x:c>
-      <x:c r="M5" s="18" t="str">
-        <x:v>Implementation / Complexity</x:v>
-      </x:c>
-      <x:c r="N5" s="18" t="str">
-        <x:v>incomplete C++ implementation; sort complexity misanalysis</x:v>
-      </x:c>
-      <x:c r="O5" s="18" t="str">
-        <x:v>vector construction / STL syntax</x:v>
-      </x:c>
-      <x:c r="P5" s="18" t="str">
-        <x:v>Valid square-then-sort idea, but no compilable C++ vector implementation. Treated sort as O(N) instead of O(N log N).</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" ht="36" hidden="0" customHeight="1">
-      <x:c r="A6" s="18" t="str">
-        <x:v>2026-09-11</x:v>
-      </x:c>
-      <x:c r="B6" s="18" t="str">
-        <x:v>Baseline Problem B</x:v>
-      </x:c>
-      <x:c r="C6" s="18" t="str">
-        <x:v>LeetCode 26 — Remove Duplicates from Sorted Array</x:v>
-      </x:c>
-      <x:c r="D6" s="18" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="E6" s="18" t="str">
-        <x:v>R2</x:v>
-      </x:c>
-      <x:c r="F6" s="18" t="str">
-        <x:v>I2</x:v>
-      </x:c>
-      <x:c r="G6" s="18" t="str">
-        <x:v>FAIL</x:v>
-      </x:c>
-      <x:c r="H6" s="18" t="n">
-        <x:v>12.383</x:v>
-      </x:c>
-      <x:c r="L6" s="18" t="str">
-        <x:v>No</x:v>
-      </x:c>
-      <x:c r="M6" s="18" t="str">
-        <x:v>Correctness / Implementation</x:v>
-      </x:c>
-      <x:c r="N6" s="18" t="str">
-        <x:v>in-place contract violation; invalid vector construction</x:v>
-      </x:c>
-      <x:c r="O6" s="18" t="str">
-        <x:v>vector construction / in-place mutation</x:v>
-      </x:c>
-      <x:c r="P6" s="18" t="str">
-        <x:v>Recognized sorted-order duplicate handling, but created a separate result vector and never rewrote nums[0..k-1], violating the required output contract.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" ht="36" hidden="0" customHeight="1">
-      <x:c r="A7" s="18" t="str">
-        <x:v>2026-09-11</x:v>
-      </x:c>
-      <x:c r="B7" s="18" t="str">
-        <x:v>Baseline Problem C</x:v>
-      </x:c>
-      <x:c r="C7" s="18" t="str">
-        <x:v>LeetCode 334 — Increasing Triplet Subsequence</x:v>
-      </x:c>
-      <x:c r="D7" s="18" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="E7" s="18" t="str">
-        <x:v>R3</x:v>
-      </x:c>
-      <x:c r="F7" s="18" t="str">
-        <x:v>I2</x:v>
-      </x:c>
-      <x:c r="G7" s="18" t="str">
-        <x:v>FAIL</x:v>
-      </x:c>
-      <x:c r="H7" s="18" t="n">
-        <x:v>112.183</x:v>
-      </x:c>
-      <x:c r="L7" s="18" t="str">
-        <x:v>No</x:v>
-      </x:c>
-      <x:c r="M7" s="18" t="str">
-        <x:v>Correctness / Implementation</x:v>
-      </x:c>
-      <x:c r="N7" s="18" t="str">
-        <x:v>incorrect invariant; false positive; bitwise XOR used as exponent; invalid vector initialization; stale candidate variables</x:v>
-      </x:c>
-      <x:c r="O7" s="18" t="str">
-        <x:v>C++ vector initialization; operator semantics (^ is XOR, not exponentiation)</x:v>
-      </x:c>
-      <x:c r="P7" s="18" t="str">
-        <x:v>O(N) and O(1) complexity analysis matches intended state size, but the algorithm is structurally incorrect. Counterexample: [1,2,1,2] can trigger true although no strictly increasing triplet exists.</x:v>
+      <x:c r="N7" t="str">
+        <x:v>incorrect invariant; operator/vector syntax</x:v>
+      </x:c>
+      <x:c r="O7" t="str">
+        <x:v>C++ semantics + invariant validation</x:v>
+      </x:c>
+      <x:c r="P7" t="str">
+        <x:v>O(N)/O(1) intent.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -1578,61 +1551,46 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
-  <x:cols>
-    <x:col min="1" max="1" width="14" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="28" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="10" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="14" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="16" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="14" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="22" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="24" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="24" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="22" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="20" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="16" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="45" hidden="0" customWidth="1"/>
-  </x:cols>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" s="14" t="str">
+      <x:c r="A1" t="str">
         <x:v>Date</x:v>
       </x:c>
-      <x:c r="B1" s="14" t="str">
-        <x:v>Target Test Profile</x:v>
-      </x:c>
-      <x:c r="C1" s="14" t="str">
+      <x:c r="B1" t="str">
+        <x:v>Name</x:v>
+      </x:c>
+      <x:c r="C1" t="str">
         <x:v>Formal?</x:v>
       </x:c>
-      <x:c r="D1" s="14" t="str">
-        <x:v>Problem Count</x:v>
-      </x:c>
-      <x:c r="E1" s="14" t="str">
-        <x:v>Time Limit (min)</x:v>
-      </x:c>
-      <x:c r="F1" s="14" t="str">
-        <x:v>C++ Standard</x:v>
-      </x:c>
-      <x:c r="G1" s="14" t="str">
-        <x:v>Compiler / Execution</x:v>
-      </x:c>
-      <x:c r="H1" s="14" t="str">
-        <x:v>Documentation / Internet</x:v>
-      </x:c>
-      <x:c r="I1" s="14" t="str">
-        <x:v>Scoring / Pass Threshold</x:v>
-      </x:c>
-      <x:c r="J1" s="14" t="str">
-        <x:v>Format</x:v>
-      </x:c>
-      <x:c r="K1" s="14" t="str">
-        <x:v>Multiple Submissions</x:v>
-      </x:c>
-      <x:c r="L1" s="14" t="str">
+      <x:c r="D1" t="str">
+        <x:v>Profile</x:v>
+      </x:c>
+      <x:c r="E1" t="str">
+        <x:v>Problems</x:v>
+      </x:c>
+      <x:c r="F1" t="str">
+        <x:v>Time Limit</x:v>
+      </x:c>
+      <x:c r="G1" t="str">
         <x:v>Result</x:v>
       </x:c>
-      <x:c r="M1" s="14" t="str">
+      <x:c r="H1" t="str">
+        <x:v>Score</x:v>
+      </x:c>
+      <x:c r="I1" t="str">
+        <x:v>First-pass Correct</x:v>
+      </x:c>
+      <x:c r="J1" t="str">
+        <x:v>Hints</x:v>
+      </x:c>
+      <x:c r="K1" t="str">
+        <x:v>Environment</x:v>
+      </x:c>
+      <x:c r="L1" t="str">
         <x:v>Notes</x:v>
+      </x:c>
+      <x:c r="M1" t="str">
+        <x:v>Source</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -1643,37 +1601,28 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
-  <x:cols>
-    <x:col min="1" max="1" width="28" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="24" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="18" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="45" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="45" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="45" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="14" hidden="0" customWidth="1"/>
-  </x:cols>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" s="14" t="str">
-        <x:v>Target Test Profile</x:v>
-      </x:c>
-      <x:c r="B1" s="14" t="str">
+      <x:c r="A1" t="str">
+        <x:v>Date</x:v>
+      </x:c>
+      <x:c r="B1" t="str">
         <x:v>Axis</x:v>
       </x:c>
-      <x:c r="C1" s="14" t="str">
+      <x:c r="C1" t="str">
         <x:v>Status</x:v>
       </x:c>
-      <x:c r="D1" s="14" t="str">
+      <x:c r="D1" t="str">
         <x:v>Evidence</x:v>
       </x:c>
-      <x:c r="E1" s="14" t="str">
+      <x:c r="E1" t="str">
         <x:v>Blocking Gaps</x:v>
       </x:c>
-      <x:c r="F1" s="14" t="str">
+      <x:c r="F1" t="str">
         <x:v>Next Action</x:v>
       </x:c>
-      <x:c r="G1" s="14" t="str">
-        <x:v>Last Updated</x:v>
+      <x:c r="G1" t="str">
+        <x:v>Notes</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -1684,134 +1633,134 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
-  <x:cols>
-    <x:col min="1" max="1" width="28" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="38" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="60" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="14" hidden="0" customWidth="1"/>
-  </x:cols>
   <x:sheetData>
-    <x:row r="1" ht="30" hidden="0" customHeight="1">
-      <x:c r="A1" s="14" t="str">
+    <x:row r="1">
+      <x:c r="A1" t="str">
         <x:v>CP Learning Dashboard</x:v>
       </x:c>
-    </x:row>
-    <x:row r="3" ht="30" hidden="0" customHeight="1">
-      <x:c r="A3" s="14" t="str">
+      <x:c r="B1"/>
+      <x:c r="C1"/>
+      <x:c r="D1"/>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2"/>
+      <x:c r="B2"/>
+      <x:c r="C2"/>
+      <x:c r="D2"/>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" t="str">
         <x:v>Metric</x:v>
       </x:c>
-      <x:c r="B3" s="14" t="str">
+      <x:c r="B3" t="str">
         <x:v>Current Value</x:v>
       </x:c>
-      <x:c r="C3" s="14" t="str">
+      <x:c r="C3" t="str">
         <x:v>Evidence / Note</x:v>
       </x:c>
-      <x:c r="D3" s="14" t="str">
+      <x:c r="D3" t="str">
         <x:v>Last Updated</x:v>
       </x:c>
     </x:row>
-    <x:row r="4" ht="30" hidden="0" customHeight="1">
-      <x:c r="A4" s="18" t="str">
+    <x:row r="4">
+      <x:c r="A4" t="str">
         <x:v>Current Stage</x:v>
       </x:c>
-      <x:c r="B4" s="18" t="str">
+      <x:c r="B4" t="str">
         <x:v>Stage 0</x:v>
       </x:c>
-      <x:c r="C4" s="18" t="str">
-        <x:v>S0-A Part F passed; Part G next</x:v>
-      </x:c>
-      <x:c r="D4" s="18" t="str">
-        <x:v>2026-09-11</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5" ht="30" hidden="0" customHeight="1">
-      <x:c r="A5" s="18" t="str">
+      <x:c r="C4" t="str">
+        <x:v>S0-A complete; S0-B next</x:v>
+      </x:c>
+      <x:c r="D4" t="str">
+        <x:v>2026-09-11</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" t="str">
         <x:v>Current Learning Unit</x:v>
       </x:c>
-      <x:c r="B5" s="18" t="str">
-        <x:v>S0-A — C++ Basic Execution</x:v>
-      </x:c>
-      <x:c r="C5" s="18" t="str">
-        <x:v>Part E PASS + Part F PASS; mandatory Adaptive Extra Problem pending</x:v>
-      </x:c>
-      <x:c r="D5" s="18" t="str">
-        <x:v>2026-09-11</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" ht="30" hidden="0" customHeight="1">
-      <x:c r="A6" s="18" t="str">
-        <x:v>Baseline independent range</x:v>
-      </x:c>
-      <x:c r="B6" s="18" t="str">
-        <x:v>R1/I1 reliable; R2 reasoning partial; R3 not yet solved</x:v>
-      </x:c>
-      <x:c r="C6" s="18" t="str">
-        <x:v>Approximate snapshot, not a fixed ceiling</x:v>
-      </x:c>
-      <x:c r="D6" s="18" t="str">
-        <x:v>2026-09-11</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" ht="30" hidden="0" customHeight="1">
-      <x:c r="A7" s="18" t="str">
-        <x:v>Primary knowledge gap</x:v>
-      </x:c>
-      <x:c r="B7" s="18" t="str">
+      <x:c r="B5" t="str">
+        <x:v>S0-B — Basic Containers &amp; STL</x:v>
+      </x:c>
+      <x:c r="C5" t="str">
+        <x:v>S0-A progression gate satisfied</x:v>
+      </x:c>
+      <x:c r="D5" t="str">
+        <x:v>2026-09-11</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" t="str">
+        <x:v>S0-A Mastery</x:v>
+      </x:c>
+      <x:c r="B6" t="str">
+        <x:v>L3 / Provisional</x:v>
+      </x:c>
+      <x:c r="C6" t="str">
+        <x:v>Part E PASS + Part F PASS + Part G PASS</x:v>
+      </x:c>
+      <x:c r="D6" t="str">
+        <x:v>2026-09-11</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" t="str">
+        <x:v>Review Debt</x:v>
+      </x:c>
+      <x:c r="B7" t="str">
+        <x:v>0 Open</x:v>
+      </x:c>
+      <x:c r="C7" t="str">
+        <x:v>Prior Medium debt resolved</x:v>
+      </x:c>
+      <x:c r="D7" t="str">
+        <x:v>2026-09-11</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" t="str">
+        <x:v>Primary next gap</x:v>
+      </x:c>
+      <x:c r="B8" t="str">
         <x:v>vector/STL implementation</x:v>
       </x:c>
-      <x:c r="C7" s="18" t="str">
-        <x:v>Observed in Baseline Problems A and B; addressed later in S0-B</x:v>
-      </x:c>
-      <x:c r="D7" s="18" t="str">
-        <x:v>2026-09-11</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" ht="30" hidden="0" customHeight="1">
-      <x:c r="A8" s="18" t="str">
-        <x:v>Primary reasoning gap</x:v>
-      </x:c>
-      <x:c r="B8" s="18" t="str">
-        <x:v>boundary / initial-state correctness + counterexample validation</x:v>
-      </x:c>
-      <x:c r="C8" s="18" t="str">
-        <x:v>Immediate remediation succeeded; monitor for recurrence in delayed/mixed evidence</x:v>
-      </x:c>
-      <x:c r="D8" s="18" t="str">
-        <x:v>2026-09-11</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" ht="30" hidden="0" customHeight="1">
-      <x:c r="A9" s="18" t="str">
-        <x:v>Current S0-A diagnostic</x:v>
-      </x:c>
-      <x:c r="B9" s="18" t="str">
-        <x:v>Final Retest 2 PASS — L3 Provisional</x:v>
-      </x:c>
-      <x:c r="C9" s="18" t="str">
-        <x:v>T_solve 33:04; explicit N=1 edge-case check; proceed to Part G</x:v>
-      </x:c>
-      <x:c r="D9" s="18" t="str">
-        <x:v>2026-09-11</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" ht="30" hidden="0" customHeight="1">
-      <x:c r="A10" s="18" t="str">
-        <x:v>Review Debt</x:v>
-      </x:c>
-      <x:c r="B10" s="18" t="str">
-        <x:v>0 Open</x:v>
-      </x:c>
-      <x:c r="C10" s="18" t="str">
-        <x:v>Prior Medium S0-A boundary/edge-case debt resolved after remediation + clean final retest</x:v>
-      </x:c>
-      <x:c r="D10" s="18" t="str">
+      <x:c r="C8" t="str">
+        <x:v>Focus of S0-B</x:v>
+      </x:c>
+      <x:c r="D8" t="str">
+        <x:v>2026-09-11</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" t="str">
+        <x:v>Delayed review</x:v>
+      </x:c>
+      <x:c r="B9" t="str">
+        <x:v>S0-A pending</x:v>
+      </x:c>
+      <x:c r="C9" t="str">
+        <x:v>Needed for Confirmed</x:v>
+      </x:c>
+      <x:c r="D9" t="str">
+        <x:v>2026-09-11</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" t="str">
+        <x:v>Baseline comparison</x:v>
+      </x:c>
+      <x:c r="B10" t="str">
+        <x:v>4–6 weeks later</x:v>
+      </x:c>
+      <x:c r="C10" t="str">
+        <x:v>Fresh equivalent problems</x:v>
+      </x:c>
+      <x:c r="D10" t="str">
         <x:v>2026-09-11</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:mergeCells>
-    <x:mergeCell ref="A1:D1"/>
-  </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
 </file>
--- a/records/CP_Learning_Record.xlsx
+++ b/records/CP_Learning_Record.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reference" sheetId="1" r:id="R8ad13d86ec39459a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Assessments" sheetId="2" r:id="R7eeb04ecba7d4d5d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mastery" sheetId="3" r:id="Rc7eb261593a148e1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decision_Coverage" sheetId="4" r:id="Rccbb99da83d04601"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Review_Debt" sheetId="5" r:id="Rc0e039fe131947f5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Baseline" sheetId="6" r:id="R3f032ec8ed70490a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mocks" sheetId="7" r:id="R41c476ae61a94407"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Readiness" sheetId="8" r:id="R86ef23a71c7e4797"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="9" r:id="Rf2f0dd9dc43149fe"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reference" sheetId="1" r:id="Rc1fde03d620a457c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Assessments" sheetId="2" r:id="Red9d9ae3f57747b7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mastery" sheetId="3" r:id="Rdf3950e533bd470f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decision_Coverage" sheetId="4" r:id="R883d7ccf99544bc2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Review_Debt" sheetId="5" r:id="R24e865e178134c4d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Baseline" sheetId="6" r:id="R455cdf781ea04a7d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mocks" sheetId="7" r:id="R3db2977d84724d5d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Readiness" sheetId="8" r:id="R367ac3c819f74f45"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="9" r:id="R7bf74ed596dc4e60"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -924,6 +924,92 @@
         <x:v>Part G PASS; explicit N=1 checks; S0-A A-H complete.</x:v>
       </x:c>
     </x:row>
+    <x:row r="8">
+      <x:c r="A8" t="str">
+        <x:v>2026-09-15</x:v>
+      </x:c>
+      <x:c r="B8" t="str">
+        <x:v>S0-B — Basic Containers &amp; STL</x:v>
+      </x:c>
+      <x:c r="C8" t="str">
+        <x:v>Intermediate Assessment — Attempt 1</x:v>
+      </x:c>
+      <x:c r="D8" t="str">
+        <x:v>Word Catalog — length then lexicographic sort; duplicates preserved</x:v>
+      </x:c>
+      <x:c r="E8" t="str">
+        <x:v>B</x:v>
+      </x:c>
+      <x:c r="F8" t="str">
+        <x:v>Prevalidated reference + exhaustive/random differential; submitted C++17 compiled + sample/random differential</x:v>
+      </x:c>
+      <x:c r="G8" t="str">
+        <x:v>R1</x:v>
+      </x:c>
+      <x:c r="H8" t="str">
+        <x:v>I2</x:v>
+      </x:c>
+      <x:c r="I8" t="str">
+        <x:v>Comparative</x:v>
+      </x:c>
+      <x:c r="J8" t="str">
+        <x:v>v1.1</x:v>
+      </x:c>
+      <x:c r="K8" t="str">
+        <x:v>vector/string + custom comparator + sort + duplicate preservation</x:v>
+      </x:c>
+      <x:c r="L8" t="str">
+        <x:v>Incomplete — Intermediate PASS; final not yet assessed</x:v>
+      </x:c>
+      <x:c r="M8" t="str">
+        <x:v>Immediate</x:v>
+      </x:c>
+      <x:c r="N8"/>
+      <x:c r="O8" t="n">
+        <x:v>10.2833</x:v>
+      </x:c>
+      <x:c r="P8"/>
+      <x:c r="Q8"/>
+      <x:c r="R8"/>
+      <x:c r="S8"/>
+      <x:c r="T8"/>
+      <x:c r="U8" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="V8" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="W8" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="X8" t="str">
+        <x:v>N/A</x:v>
+      </x:c>
+      <x:c r="Y8" t="str">
+        <x:v>None — minor explanation wording imprecision; signed/unsigned warning only</x:v>
+      </x:c>
+      <x:c r="Z8" t="str">
+        <x:v>L3</x:v>
+      </x:c>
+      <x:c r="AA8" t="str">
+        <x:v>Provisional</x:v>
+      </x:c>
+      <x:c r="AB8" t="str">
+        <x:v>Immediate</x:v>
+      </x:c>
+      <x:c r="AC8" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="AD8" t="str">
+        <x:v>N/A</x:v>
+      </x:c>
+      <x:c r="AE8" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="AF8" t="str">
+        <x:v>Correct code. Comparator uses length ascending then lexicographic ascending; duplicates retained. O(N log N) time and O(N) storage are valid with max string length 30. Explanation briefly said 'strings differ' where code checks 'lengths differ'; no correctness impact.</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -1032,16 +1118,16 @@
         <x:v>Core</x:v>
       </x:c>
       <x:c r="D3" t="str">
-        <x:v>L1</x:v>
+        <x:v>L3</x:v>
       </x:c>
       <x:c r="E3" t="str">
         <x:v>Provisional</x:v>
       </x:c>
       <x:c r="F3" t="str">
-        <x:v>Baseline</x:v>
+        <x:v>Immediate</x:v>
       </x:c>
       <x:c r="G3" t="str">
-        <x:v>N/A</x:v>
+        <x:v>Intermediate PASS; Final not yet assessed</x:v>
       </x:c>
       <x:c r="H3" t="str">
         <x:v>None</x:v>
@@ -1050,19 +1136,19 @@
         <x:v>N/A</x:v>
       </x:c>
       <x:c r="J3" t="str">
-        <x:v>Yes</x:v>
+        <x:v>No</x:v>
       </x:c>
       <x:c r="K3" t="str">
-        <x:v>2026-09-11</x:v>
+        <x:v>2026-09-15</x:v>
       </x:c>
       <x:c r="L3" t="str">
-        <x:v>During S0-B</x:v>
+        <x:v>Final Assessment</x:v>
       </x:c>
       <x:c r="M3" t="str">
-        <x:v>vector/STL syntax and manipulation</x:v>
+        <x:v>Broader container/STL selection and transfer evidence still pending</x:v>
       </x:c>
       <x:c r="N3" t="str">
-        <x:v>Baseline A/B exposed gap.</x:v>
+        <x:v>Part E intermediate assessment PASS; canonical vector/string/sort/comparator implementation independently demonstrated.</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
@@ -1670,10 +1756,10 @@
         <x:v>Stage 0</x:v>
       </x:c>
       <x:c r="C4" t="str">
-        <x:v>S0-A complete; S0-B next</x:v>
+        <x:v>S0-B Part E intermediate PASS; final pending</x:v>
       </x:c>
       <x:c r="D4" t="str">
-        <x:v>2026-09-11</x:v>
+        <x:v>2026-09-15</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -1684,10 +1770,10 @@
         <x:v>S0-B — Basic Containers &amp; STL</x:v>
       </x:c>
       <x:c r="C5" t="str">
-        <x:v>S0-A progression gate satisfied</x:v>
+        <x:v>Intermediate assessment PASS</x:v>
       </x:c>
       <x:c r="D5" t="str">
-        <x:v>2026-09-11</x:v>
+        <x:v>2026-09-15</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
@@ -1723,13 +1809,13 @@
         <x:v>Primary next gap</x:v>
       </x:c>
       <x:c r="B8" t="str">
-        <x:v>vector/STL implementation</x:v>
+        <x:v>S0-B final/transfer evidence</x:v>
       </x:c>
       <x:c r="C8" t="str">
-        <x:v>Focus of S0-B</x:v>
+        <x:v>Broader container/STL selection still unverified</x:v>
       </x:c>
       <x:c r="D8" t="str">
-        <x:v>2026-09-11</x:v>
+        <x:v>2026-09-15</x:v>
       </x:c>
     </x:row>
     <x:row r="9">

--- a/records/CP_Learning_Record.xlsx
+++ b/records/CP_Learning_Record.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reference" sheetId="1" r:id="Rc1fde03d620a457c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Assessments" sheetId="2" r:id="Red9d9ae3f57747b7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mastery" sheetId="3" r:id="Rdf3950e533bd470f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decision_Coverage" sheetId="4" r:id="R883d7ccf99544bc2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Review_Debt" sheetId="5" r:id="R24e865e178134c4d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Baseline" sheetId="6" r:id="R455cdf781ea04a7d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mocks" sheetId="7" r:id="R3db2977d84724d5d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Readiness" sheetId="8" r:id="R367ac3c819f74f45"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="9" r:id="R7bf74ed596dc4e60"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reference" sheetId="1" r:id="Rb18e490d2c984bf8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Assessments" sheetId="2" r:id="R2156b0472a624a0e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mastery" sheetId="3" r:id="Rba349085c8ef47ef"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decision_Coverage" sheetId="4" r:id="Redfb30ba205e4f14"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Review_Debt" sheetId="5" r:id="Rc2eb5380fd2544ba"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Baseline" sheetId="6" r:id="R956115e8de324a7b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mocks" sheetId="7" r:id="R8e9fdde10bdf4bd2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Readiness" sheetId="8" r:id="Rd5bb143737c346cb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="9" r:id="R12025444ee744ee2"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1010,6 +1010,92 @@
         <x:v>Correct code. Comparator uses length ascending then lexicographic ascending; duplicates retained. O(N log N) time and O(N) storage are valid with max string length 30. Explanation briefly said 'strings differ' where code checks 'lengths differ'; no correctness impact.</x:v>
       </x:c>
     </x:row>
+    <x:row r="9">
+      <x:c r="A9" t="str">
+        <x:v>2026-09-15</x:v>
+      </x:c>
+      <x:c r="B9" t="str">
+        <x:v>S0-B — Basic Containers &amp; STL</x:v>
+      </x:c>
+      <x:c r="C9" t="str">
+        <x:v>Final Assessment — Attempt 1</x:v>
+      </x:c>
+      <x:c r="D9" t="str">
+        <x:v>Priority List — priority desc, length asc, lexicographic asc; forward + exact reverse</x:v>
+      </x:c>
+      <x:c r="E9" t="str">
+        <x:v>B</x:v>
+      </x:c>
+      <x:c r="F9" t="str">
+        <x:v>Prevalidated reference + exhaustive/random differential; submitted C++17 compiled + sample output; explicit contract audit</x:v>
+      </x:c>
+      <x:c r="G9" t="str">
+        <x:v>R1</x:v>
+      </x:c>
+      <x:c r="H9" t="str">
+        <x:v>I2</x:v>
+      </x:c>
+      <x:c r="I9" t="str">
+        <x:v>Comparative / Provisional</x:v>
+      </x:c>
+      <x:c r="J9" t="str">
+        <x:v>v1.1</x:v>
+      </x:c>
+      <x:c r="K9" t="str">
+        <x:v>vector&lt;pair&lt;string,int&gt;&gt; + custom comparator + sort/reverse + const-reference output-helper contract</x:v>
+      </x:c>
+      <x:c r="L9" t="str">
+        <x:v>Incomplete — Final FAIL; retest required</x:v>
+      </x:c>
+      <x:c r="M9" t="str">
+        <x:v>Immediate</x:v>
+      </x:c>
+      <x:c r="N9"/>
+      <x:c r="O9" t="n">
+        <x:v>24.3333</x:v>
+      </x:c>
+      <x:c r="P9"/>
+      <x:c r="Q9"/>
+      <x:c r="R9"/>
+      <x:c r="S9"/>
+      <x:c r="T9"/>
+      <x:c r="U9" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="V9" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="W9" t="str">
+        <x:v>FAIL</x:v>
+      </x:c>
+      <x:c r="X9" t="str">
+        <x:v>Implementation</x:v>
+      </x:c>
+      <x:c r="Y9" t="str">
+        <x:v>Required print_records output function not implemented; comparator was named print_records instead. Container const-reference output interface therefore not demonstrated. Non-void comparator also emits fallthrough warning.</x:v>
+      </x:c>
+      <x:c r="Z9" t="str">
+        <x:v>L3</x:v>
+      </x:c>
+      <x:c r="AA9" t="str">
+        <x:v>Provisional</x:v>
+      </x:c>
+      <x:c r="AB9" t="str">
+        <x:v>Immediate</x:v>
+      </x:c>
+      <x:c r="AC9" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="AD9" t="str">
+        <x:v>N/A</x:v>
+      </x:c>
+      <x:c r="AE9" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="AF9" t="str">
+        <x:v>Sorting/output values are correct and complexity target is met, but an explicit assessed interface requirement was structurally missed. Same problem is now learning-only; use a new equivalent problem for retest.</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -1127,7 +1213,7 @@
         <x:v>Immediate</x:v>
       </x:c>
       <x:c r="G3" t="str">
-        <x:v>Intermediate PASS; Final not yet assessed</x:v>
+        <x:v>Intermediate PASS; Final Attempt 1 FAIL — retest required</x:v>
       </x:c>
       <x:c r="H3" t="str">
         <x:v>None</x:v>
@@ -1136,19 +1222,19 @@
         <x:v>N/A</x:v>
       </x:c>
       <x:c r="J3" t="str">
-        <x:v>No</x:v>
+        <x:v>Yes</x:v>
       </x:c>
       <x:c r="K3" t="str">
         <x:v>2026-09-15</x:v>
       </x:c>
       <x:c r="L3" t="str">
-        <x:v>Final Assessment</x:v>
+        <x:v>Final Assessment Retest 1</x:v>
       </x:c>
       <x:c r="M3" t="str">
-        <x:v>Broader container/STL selection and transfer evidence still pending</x:v>
+        <x:v>Problem-contract/interface mapping: implement required output helper with container const-reference</x:v>
       </x:c>
       <x:c r="N3" t="str">
-        <x:v>Part E intermediate assessment PASS; canonical vector/string/sort/comparator implementation independently demonstrated.</x:v>
+        <x:v>Sorting/comparator/vector/pair/reverse logic is independently demonstrated; final attempt failed because the required print_records output function was not implemented.</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
@@ -1756,7 +1842,7 @@
         <x:v>Stage 0</x:v>
       </x:c>
       <x:c r="C4" t="str">
-        <x:v>S0-B Part E intermediate PASS; final pending</x:v>
+        <x:v>S0-B Part F final attempt 1 FAIL; retest pending</x:v>
       </x:c>
       <x:c r="D4" t="str">
         <x:v>2026-09-15</x:v>
@@ -1770,7 +1856,7 @@
         <x:v>S0-B — Basic Containers &amp; STL</x:v>
       </x:c>
       <x:c r="C5" t="str">
-        <x:v>Intermediate assessment PASS</x:v>
+        <x:v>Intermediate PASS; Final retest required</x:v>
       </x:c>
       <x:c r="D5" t="str">
         <x:v>2026-09-15</x:v>
@@ -1809,10 +1895,10 @@
         <x:v>Primary next gap</x:v>
       </x:c>
       <x:c r="B8" t="str">
-        <x:v>S0-B final/transfer evidence</x:v>
+        <x:v>S0-B interface-contract retest</x:v>
       </x:c>
       <x:c r="C8" t="str">
-        <x:v>Broader container/STL selection still unverified</x:v>
+        <x:v>Sorting logic correct; required const-ref print helper was missed</x:v>
       </x:c>
       <x:c r="D8" t="str">
         <x:v>2026-09-15</x:v>

--- a/records/CP_Learning_Record.xlsx
+++ b/records/CP_Learning_Record.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reference" sheetId="1" r:id="Rb0316a5798d54f36"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Assessments" sheetId="2" r:id="Ra12cd6f65db644ef"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mastery" sheetId="3" r:id="Raf874f697b214626"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decision_Coverage" sheetId="4" r:id="R8690db1676924cd8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Review_Debt" sheetId="5" r:id="R4097597294174885"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Baseline" sheetId="6" r:id="R9397512ebef84164"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mocks" sheetId="7" r:id="Raa43339e005e4f11"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Readiness" sheetId="8" r:id="R66f93c63fef84d5c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="9" r:id="Ra2990a0f9bc44e25"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reference" sheetId="1" r:id="Re4bd5171355a4942"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Assessments" sheetId="2" r:id="Rba6a2571d8284b7a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mastery" sheetId="3" r:id="Rcf7b571c6a7b4245"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decision_Coverage" sheetId="4" r:id="R19628492a4474f50"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Review_Debt" sheetId="5" r:id="Rbedd507439af4da6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Baseline" sheetId="6" r:id="R2aef51e4f0b24a0a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mocks" sheetId="7" r:id="R366dbf8ca5ac41ea"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Readiness" sheetId="8" r:id="R66bd2c5665034c98"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="9" r:id="R3096cc727bc04567"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1354,6 +1354,92 @@
         <x:v>Code is correct and satisfies the required normalize(vector&lt;string&gt;&amp;) in-place contract. Correct total complexity uses L=sum of word lengths: O(L) time and O(L) total storage including input, O(1) auxiliary space. One non-blocking signed/unsigned loop warning. Fresh equivalent reassessment required for the complexity-analysis objective.</x:v>
       </x:c>
     </x:row>
+    <x:row r="13">
+      <x:c r="A13" t="str">
+        <x:v>2026-09-15</x:v>
+      </x:c>
+      <x:c r="B13" t="str">
+        <x:v>S0-B — Basic Containers &amp; STL</x:v>
+      </x:c>
+      <x:c r="C13" t="str">
+        <x:v>v5.5 Extra Problem — External CP</x:v>
+      </x:c>
+      <x:c r="D13" t="str">
+        <x:v>AtCoder ABC104 B — AcCepted</x:v>
+      </x:c>
+      <x:c r="E13" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="F13" t="str">
+        <x:v>Official AtCoder judge/problem statement; submitted C++17 compiled locally; targeted counterexample audit</x:v>
+      </x:c>
+      <x:c r="G13" t="str">
+        <x:v>R1</x:v>
+      </x:c>
+      <x:c r="H13" t="str">
+        <x:v>I1</x:v>
+      </x:c>
+      <x:c r="I13" t="str">
+        <x:v>Comparative / Provisional</x:v>
+      </x:c>
+      <x:c r="J13" t="str">
+        <x:v>v1.1</x:v>
+      </x:c>
+      <x:c r="K13" t="str">
+        <x:v>string indexing + conditional validation + uppercase/lowercase checks + bounded scan</x:v>
+      </x:c>
+      <x:c r="L13" t="str">
+        <x:v>Complete — Progression Gate previously satisfied; post-completion External Extra evidence</x:v>
+      </x:c>
+      <x:c r="M13" t="str">
+        <x:v>Immediate</x:v>
+      </x:c>
+      <x:c r="N13"/>
+      <x:c r="O13" t="n">
+        <x:v>24.95</x:v>
+      </x:c>
+      <x:c r="P13"/>
+      <x:c r="Q13"/>
+      <x:c r="R13"/>
+      <x:c r="S13"/>
+      <x:c r="T13"/>
+      <x:c r="U13" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="V13" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="W13" t="str">
+        <x:v>CONDITIONAL PASS</x:v>
+      </x:c>
+      <x:c r="X13" t="str">
+        <x:v>N/A</x:v>
+      </x:c>
+      <x:c r="Y13" t="str">
+        <x:v>Local implementation bug: uppercase 'Z' is never checked because loop condition c != 'Z' stops before Z</x:v>
+      </x:c>
+      <x:c r="Z13" t="str">
+        <x:v>L3</x:v>
+      </x:c>
+      <x:c r="AA13" t="str">
+        <x:v>Provisional</x:v>
+      </x:c>
+      <x:c r="AB13" t="str">
+        <x:v>Immediate</x:v>
+      </x:c>
+      <x:c r="AC13" t="str">
+        <x:v>Open</x:v>
+      </x:c>
+      <x:c r="AD13" t="str">
+        <x:v>Low</x:v>
+      </x:c>
+      <x:c r="AE13" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="AF13" t="str">
+        <x:v>Core solution structure and O(|S|) time / O(|S|) total storage analysis are correct. One-line boundary fix is sufficient: the uppercase scan must include 'Z' (e.g. c &lt;= 'Z') or use an equivalent uppercase test. Counterexample: AcCZ should be WA but submitted code prints AC. User edge cases AccC-&gt;WA and AcCc-&gt;AC are correct. Fresh equivalent full-PASS evidence is required; this does not revoke the prior S0-B progression gate.</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -1486,13 +1572,13 @@
         <x:v>2026-09-15</x:v>
       </x:c>
       <x:c r="L3" t="str">
-        <x:v>Fresh equivalent Extra / S0-C transfer check</x:v>
+        <x:v>Fresh equivalent Extra / S0-C transfer check + mixed S0-B review</x:v>
       </x:c>
       <x:c r="M3" t="str">
-        <x:v>Complexity accounting for non-constant library operations and distinguishing N from total input size L</x:v>
+        <x:v>Primary: complexity accounting for non-constant library operations and N vs total input length L; secondary: exact boundary handling in character classification</x:v>
       </x:c>
       <x:c r="N3" t="str">
-        <x:v>A-H progression gate remains satisfied. Post-completion v5.5 GPT-generated Extra: code correct, but assessment FAIL on complexity explanation; Medium Review Debt opened. Confidence remains Provisional.</x:v>
+        <x:v>A-H progression gate remains satisfied. Post-completion v5.5 GPT-generated Extra FAIL opened Medium complexity debt. External CP Extra (AtCoder ABC104 B) received CONDITIONAL PASS: solution structure and complexity were correct, but uppercase 'Z' was omitted by a one-line loop-bound bug. An additional Low implementation debt is open. Overall debt severity remains Medium; Confidence remains Provisional.</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
@@ -1747,6 +1833,39 @@
         <x:v>Post-completion Extra FAIL does not revoke the prior S0-B progression gate; debt tracks the unresolved complexity-analysis objective.</x:v>
       </x:c>
     </x:row>
+    <x:row r="4">
+      <x:c r="A4" t="str">
+        <x:v>2026-09-15</x:v>
+      </x:c>
+      <x:c r="B4" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C4" t="str">
+        <x:v>S0-B — Basic Containers &amp; STL</x:v>
+      </x:c>
+      <x:c r="D4" t="str">
+        <x:v>Low</x:v>
+      </x:c>
+      <x:c r="E4" t="str">
+        <x:v>Local uppercase-boundary implementation bug in External Extra: 'Z' omitted from uppercase scan</x:v>
+      </x:c>
+      <x:c r="F4" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="G4" t="str">
+        <x:v>Open</x:v>
+      </x:c>
+      <x:c r="H4" t="str">
+        <x:v>Reassess exact character-boundary validation on a fresh equivalent problem; require full PASS without hints</x:v>
+      </x:c>
+      <x:c r="I4" t="str">
+        <x:v>Fresh equivalent Extra / mixed S0-B review</x:v>
+      </x:c>
+      <x:c r="J4"/>
+      <x:c r="K4" t="str">
+        <x:v>CONDITIONAL PASS creates Review Debt until a clean full PASS. Existing Medium complexity debt remains separately open.</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
